--- a/industry/industry.xlsx
+++ b/industry/industry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rideau Truck\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC45937-4719-4C38-972B-5E444C2CA7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E532C0F-E627-431A-B317-63219945B975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{5E28C574-94B7-40B9-9081-619E63A6A598}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="249">
   <si>
     <t>Year</t>
   </si>
@@ -751,9 +751,6 @@
     <t>Made-up</t>
   </si>
   <si>
-    <t>Note: subtracted estimated canned fish portion</t>
-  </si>
-  <si>
     <t>Butchery1945+Market1945</t>
   </si>
   <si>
@@ -761,6 +758,30 @@
   </si>
   <si>
     <t>New crates/mo</t>
+  </si>
+  <si>
+    <t>First report</t>
+  </si>
+  <si>
+    <t>35.89 oz/head/week</t>
+  </si>
+  <si>
+    <t>The 1960 food report gives fish consumption in "edible weight" as 26.2 lb/head/annum (or 8.03 oz/head/week), while the 1940 report appears to be working in "on the bone" weight at 13.9 oz/week</t>
+  </si>
+  <si>
+    <t>This results in a conversion factor of 57.8% for converting the 1934-35 and 1909-13 statistics listed in the 1940 report.</t>
+  </si>
+  <si>
+    <t>See note 3</t>
+  </si>
+  <si>
+    <t>The 1960 food report gives meat consumption in "edible weight" as 116.5 lb/head/annum (35.7 oz/head/week), while the 1940 report gives apparently "on the bone" weight at 45 oz/head/week</t>
+  </si>
+  <si>
+    <t>This results in a conversion factor of 79.3% for converting the 1934-35 and 1909-13 statistics.</t>
+  </si>
+  <si>
+    <t>% match</t>
   </si>
 </sst>
 </file>
@@ -822,7 +843,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -846,7 +867,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1163,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF8D15F6-18A6-495C-86EC-32003DCCF29C}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
@@ -1355,11 +1375,8 @@
         <v>89</v>
       </c>
       <c r="D12">
-        <f>(41.3/7)*10000*6.4/8</f>
-        <v>47200</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>88</v>
+        <f>(41.3/7)*0.793*10000*6.4/8</f>
+        <v>37429.599999999999</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1370,11 +1387,11 @@
         <v>90</v>
       </c>
       <c r="D13">
-        <f>(12.6/7)*10000*6.4/8*(5.35/(5.35+D52))</f>
-        <v>11246.715328467153</v>
+        <f>(12.6/7)*10000*6.4/8*0.578</f>
+        <v>8323.1999999999989</v>
       </c>
       <c r="E13" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1436,12 +1453,10 @@
         <v>96</v>
       </c>
       <c r="D18">
-        <f>(45/7)*10000*6.4/8</f>
-        <v>51428.571428571435</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>88</v>
-      </c>
+        <f>(45/7)*0.793*10000*6.4/8</f>
+        <v>40782.857142857152</v>
+      </c>
+      <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
@@ -1451,11 +1466,11 @@
         <v>97</v>
       </c>
       <c r="D19">
-        <f>((13.9/7)*10000*6.4/8)*(5.35/(5.35+D52))</f>
-        <v>12407.09071949948</v>
+        <f>((13.9/7)*10000*6.4/8)*(0.578)</f>
+        <v>9181.942857142858</v>
       </c>
       <c r="E19" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1508,601 +1523,694 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24">
-        <f xml:space="preserve"> (39.53 / 7) *10000*6.4/8</f>
-        <v>45177.14285714287</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>9</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>3</v>
       </c>
-      <c r="C25" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25">
-        <f>(5.35/7)*6.4*10000/8</f>
-        <v>6114.2857142857147</v>
-      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26">
-        <f>(63.19/7)*10000*6.4/8</f>
-        <v>72217.14285714287</v>
-      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>5</v>
       </c>
-      <c r="C27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27">
-        <f>(87.55/7)*10000*6.4/8</f>
-        <v>100057.14285714286</v>
-      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28">
-        <f>(23.14/7)*6.4*10000/8</f>
-        <v>26445.714285714286</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>72</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1970</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30">
+        <f xml:space="preserve"> (39.53 / 7) *10000*6.4/8</f>
+        <v>45177.14285714287</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31">
+        <f>(5.35/7)*6.4*10000/8</f>
+        <v>6114.2857142857147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32">
+        <f>(63.19/7)*10000*6.4/8</f>
+        <v>72217.14285714287</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33">
+        <f>(87.55/7)*10000*6.4/8</f>
+        <v>100057.14285714286</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34">
+        <f>(23.14/7)*6.4*10000/8</f>
+        <v>26445.714285714286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" t="s">
         <v>77</v>
       </c>
-      <c r="D29">
+      <c r="D35">
         <f xml:space="preserve"> (2.88676842 / 7) * 10000 * 6.4 / 8</f>
         <v>3299.1639085714291</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>213</v>
       </c>
-      <c r="D30">
-        <f>(D54/7)*10000*6.4/8</f>
+      <c r="D36">
+        <f>(D68/7)*10000*6.4/8</f>
         <v>17588.571428571431</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>2000</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B37" t="s">
         <v>2</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C37" t="s">
         <v>42</v>
       </c>
-      <c r="D31">
+      <c r="D37">
         <f>((1016*0.03527396)/7)*6.4*10000/8</f>
         <v>40958.106697142859</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>3</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C38" t="s">
         <v>44</v>
       </c>
-      <c r="D32">
-        <f>(163/1016)*D31</f>
+      <c r="D38">
+        <f>(163/1016)*D37</f>
         <v>6571.0348342857142</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C39" t="s">
         <v>46</v>
       </c>
-      <c r="D33">
-        <f>(1790/1016)*D31</f>
+      <c r="D39">
+        <f>(1790/1016)*D37</f>
         <v>72160.443885714281</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>5</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C40" t="s">
         <v>43</v>
       </c>
-      <c r="D34">
-        <f>(2140/1016)*D31</f>
+      <c r="D40">
+        <f>(2140/1016)*D37</f>
         <v>86270.027885714284</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>85</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C41" t="s">
         <v>86</v>
       </c>
-      <c r="D35">
-        <f>(761/1016)*D31</f>
+      <c r="D41">
+        <f>(761/1016)*D37</f>
         <v>30678.266925714288</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D42" s="6">
         <f>(2.156/7)*10000*6.4/8</f>
         <v>2464</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>213</v>
       </c>
-      <c r="D37" s="6">
-        <f>((B54*0.03527396) / 7)*10000*6.4/8</f>
+      <c r="D43" s="6">
+        <f>((B68*0.03527396) / 7)*10000*6.4/8</f>
         <v>42852.822262857146</v>
       </c>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="4"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="B44" s="3"/>
+      <c r="C44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>1</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>2</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B46" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>3</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B47" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>1</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B49" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>2</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B50" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>2</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>202</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B60" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>223</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C63" t="s">
         <v>201</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D63" t="s">
         <v>214</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E63" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>199</v>
       </c>
-      <c r="B50">
+      <c r="B64">
         <f>45+126+256</f>
         <v>427</v>
       </c>
-      <c r="C50">
-        <f>B50/B$54</f>
+      <c r="C64">
+        <f>B64/B$68</f>
         <v>0.40169332079021636</v>
       </c>
-      <c r="D50">
+      <c r="D64">
         <f>0.94+0.22+0.71+1.98</f>
         <v>3.8499999999999996</v>
       </c>
-      <c r="E50">
-        <f>D50/D$54</f>
+      <c r="E64">
+        <f>D64/D$68</f>
         <v>0.25016244314489927</v>
       </c>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>231</v>
       </c>
-      <c r="B51">
+      <c r="B65">
         <f>360+85</f>
         <v>445</v>
       </c>
-      <c r="C51">
-        <f>B51/B$54</f>
+      <c r="C65">
+        <f>B65/B$68</f>
         <v>0.41862652869238004</v>
       </c>
-      <c r="D51">
+      <c r="D65">
         <f>2.32+2.29+0.56+1.28</f>
         <v>6.45</v>
       </c>
-      <c r="E51">
-        <f>D51/D$54</f>
+      <c r="E65">
+        <f>D65/D$68</f>
         <v>0.41910331384015592</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>200</v>
       </c>
-      <c r="B52">
+      <c r="B66">
         <f>6+31+44</f>
         <v>81</v>
       </c>
-      <c r="C52">
-        <f>B52/B$54</f>
+      <c r="C66">
+        <f>B66/B$68</f>
         <v>7.61994355597366E-2</v>
       </c>
-      <c r="D52">
+      <c r="D66">
         <f>0.38+0.31+0.14+0.67</f>
         <v>1.5</v>
       </c>
-      <c r="E52">
-        <f>D52/D$54</f>
+      <c r="E66">
+        <f>D66/D$68</f>
         <v>9.7465886939571145E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>204</v>
       </c>
-      <c r="B53">
+      <c r="B67">
         <v>110</v>
       </c>
-      <c r="C53">
-        <f>B53/B$54</f>
+      <c r="C67">
+        <f>B67/B$68</f>
         <v>0.10348071495766697</v>
       </c>
-      <c r="D53">
+      <c r="D67">
         <v>3.59</v>
       </c>
-      <c r="E53">
-        <f>D53/D$54</f>
+      <c r="E67">
+        <f>D67/D$68</f>
         <v>0.23326835607537361</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>206</v>
       </c>
-      <c r="B54" s="1">
-        <f>SUM(B50:B53)</f>
+      <c r="B68" s="1">
+        <f>SUM(B64:B67)</f>
         <v>1063</v>
       </c>
-      <c r="D54" s="1">
-        <f>SUM(D50:D53)</f>
+      <c r="D68" s="1">
+        <f>SUM(D64:D67)</f>
         <v>15.39</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>232</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B70" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C74" t="s">
         <v>18</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D74" t="s">
         <v>221</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E74" t="s">
         <v>212</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F74" t="s">
         <v>198</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G74" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B75" t="s">
         <v>2</v>
       </c>
-      <c r="C61">
+      <c r="C75">
         <v>103</v>
       </c>
-      <c r="D61">
-        <f>(C61/C$65)*100</f>
+      <c r="D75">
+        <f>(C75/C$79)*100</f>
         <v>32.698412698412696</v>
       </c>
-      <c r="E61">
+      <c r="E75">
         <v>4</v>
       </c>
-      <c r="F61" s="1">
-        <f>ROUND(((C50*100)/D61)*E61, 0)</f>
+      <c r="F75" s="1">
+        <f>ROUND(((C64*100)/D75)*E75, 0)</f>
         <v>5</v>
       </c>
-      <c r="G61">
-        <f>ROUND(F61/SUM(F$61:F$64)*E$65,0)</f>
+      <c r="G75">
+        <f>ROUND(F75/SUM(F$75:F$78)*E$79,0)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>218</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B76" t="s">
         <v>6</v>
       </c>
-      <c r="C62">
+      <c r="C76">
         <v>103</v>
       </c>
-      <c r="D62">
-        <f>(C62/C$65)*100</f>
+      <c r="D76">
+        <f>(C76/C$79)*100</f>
         <v>32.698412698412696</v>
       </c>
-      <c r="E62">
+      <c r="E76">
         <v>6</v>
       </c>
-      <c r="F62" s="1">
-        <f>ROUND(((C51*100)/D62)*E62, 0)</f>
+      <c r="F76" s="1">
+        <f>ROUND(((C65*100)/D76)*E76, 0)</f>
         <v>8</v>
       </c>
-      <c r="G62">
-        <f>ROUND(F62/SUM(F$61:F$64)*E$65,0)</f>
+      <c r="G76">
+        <f>ROUND(F76/SUM(F$75:F$78)*E$79,0)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B77" t="s">
         <v>3</v>
       </c>
-      <c r="C63">
+      <c r="C77">
         <v>103</v>
       </c>
-      <c r="D63">
-        <f>(C63/C$65)*100</f>
+      <c r="D77">
+        <f>(C77/C$79)*100</f>
         <v>32.698412698412696</v>
       </c>
-      <c r="E63">
+      <c r="E77">
         <v>4</v>
       </c>
-      <c r="F63" s="1">
-        <f>ROUND(((C52*100)/D63)*E63, 0)</f>
+      <c r="F77" s="1">
+        <f>ROUND(((C66*100)/D77)*E77, 0)</f>
         <v>1</v>
       </c>
-      <c r="G63">
-        <f>ROUND(F63/SUM(F$61:F$64)*E$65,0)</f>
+      <c r="G77">
+        <f>ROUND(F77/SUM(F$75:F$78)*E$79,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B78" t="s">
         <v>208</v>
       </c>
-      <c r="C64">
+      <c r="C78">
         <v>6</v>
       </c>
-      <c r="D64">
-        <f>(C64/C$65)*100</f>
+      <c r="D78">
+        <f>(C78/C$79)*100</f>
         <v>1.9047619047619049</v>
       </c>
-      <c r="E64">
+      <c r="E78">
         <v>4</v>
       </c>
-      <c r="F64" s="1">
-        <f>ROUND(((C53*100)/D64)*E64, 0)</f>
+      <c r="F78" s="1">
+        <f>ROUND(((C67*100)/D78)*E78, 0)</f>
         <v>22</v>
       </c>
-      <c r="G64">
-        <f>ROUND(F64/SUM(F$61:F$64)*E$65,0)</f>
+      <c r="G78">
+        <f>ROUND(F78/SUM(F$75:F$78)*E$79,0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C65" s="1">
-        <f>SUM(C61:C64)</f>
+      <c r="C79" s="1">
+        <f>SUM(C75:C78)</f>
         <v>315</v>
       </c>
-      <c r="E65">
-        <f>SUM(E61:E64)</f>
+      <c r="E79">
+        <f>SUM(E75:E78)</f>
         <v>18</v>
       </c>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>216</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B80" t="s">
         <v>2</v>
       </c>
-      <c r="C66">
+      <c r="C80">
         <v>103</v>
       </c>
-      <c r="D66">
-        <f>(C66/C$70)*100</f>
+      <c r="D80">
+        <f>(C80/C$84)*100</f>
         <v>32.924178493798749</v>
       </c>
-      <c r="E66">
+      <c r="E80">
         <v>6</v>
       </c>
-      <c r="F66" s="1">
-        <f>ROUND(((E50*100)/D66)*E66, 0)</f>
+      <c r="F80" s="1">
+        <f>ROUND(((E64*100)/D80)*E80, 0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>217</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B81" t="s">
         <v>6</v>
       </c>
-      <c r="C67">
+      <c r="C81">
         <v>103</v>
       </c>
-      <c r="D67">
-        <f>(C67/C$70)*100</f>
+      <c r="D81">
+        <f>(C81/C$84)*100</f>
         <v>32.924178493798749</v>
       </c>
-      <c r="E67">
+      <c r="E81">
         <v>9</v>
       </c>
-      <c r="F67" s="1">
-        <f>ROUND(((E51*100)/D67)*E67, 0)</f>
+      <c r="F81" s="1">
+        <f>ROUND(((E65*100)/D81)*E81, 0)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>220</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B82" t="s">
         <v>3</v>
       </c>
-      <c r="C68">
+      <c r="C82">
         <v>103</v>
       </c>
-      <c r="D68">
-        <f>(C68/C$70)*100</f>
+      <c r="D82">
+        <f>(C82/C$84)*100</f>
         <v>32.924178493798749</v>
       </c>
-      <c r="E68">
+      <c r="E82">
         <v>6</v>
       </c>
-      <c r="F68" s="1">
-        <f>ROUND(((E52*100)/D68)*E68, 0)</f>
+      <c r="F82" s="1">
+        <f>ROUND(((E66*100)/D82)*E82, 0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>215</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B83" t="s">
         <v>208</v>
       </c>
-      <c r="C69">
+      <c r="C83">
         <v>3.84</v>
       </c>
-      <c r="D69">
-        <f>(C69/C$70)*100</f>
+      <c r="D83">
+        <f>(C83/C$84)*100</f>
         <v>1.2274645186037592</v>
       </c>
-      <c r="E69">
+      <c r="E83">
         <v>6</v>
       </c>
-      <c r="F69" s="1">
-        <f>ROUND(((E53*100)/D69)*E69, 0)</f>
+      <c r="F83" s="1">
+        <f>ROUND(((E67*100)/D83)*E83, 0)</f>
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C70" s="1">
-        <f>SUM(C66:C69)</f>
+      <c r="C84" s="1">
+        <f>SUM(C80:C83)</f>
         <v>312.83999999999997</v>
       </c>
-      <c r="E70" s="1">
-        <f>SUM(E66:E69)</f>
+      <c r="E84" s="1">
+        <f>SUM(E80:E83)</f>
         <v>27</v>
       </c>
     </row>
@@ -2110,16 +2218,16 @@
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://history.pictures/2020/02/10/9-3-consumption-of-meat/" xr:uid="{F6ABE5C8-37CB-4716-879B-64C74DB128F8}"/>
     <hyperlink ref="E9" r:id="rId2" display="https://history.pictures/2020/02/10/9-3-consumption-of-meat/" xr:uid="{0EE12F9B-C523-4FAF-AA87-223AD63C33E5}"/>
-    <hyperlink ref="E24" r:id="rId3" xr:uid="{731C3305-BEAA-4468-BD29-D135D35C5112}"/>
-    <hyperlink ref="E31" r:id="rId4" display="https://webarchive.nationalarchives.gov.uk/ukgwa/20130104055333mp_/http:/www.defra.gov.uk/statistics/files/defra-stats-food-family-annual-2002.pdf" xr:uid="{D65896A6-5EDA-45A1-BFDD-E3DD440364A5}"/>
+    <hyperlink ref="E30" r:id="rId3" xr:uid="{731C3305-BEAA-4468-BD29-D135D35C5112}"/>
+    <hyperlink ref="E37" r:id="rId4" display="https://webarchive.nationalarchives.gov.uk/ukgwa/20130104055333mp_/http:/www.defra.gov.uk/statistics/files/defra-stats-food-family-annual-2002.pdf" xr:uid="{D65896A6-5EDA-45A1-BFDD-E3DD440364A5}"/>
     <hyperlink ref="E8" r:id="rId5" display="https://history.pictures/2020/10/21/9-4-consumption-of-other-foods/" xr:uid="{B5BDB095-F4AA-4AEC-BED2-835552E677DA}"/>
     <hyperlink ref="E5" r:id="rId6" display="https://history.pictures/2020/10/21/9-4-consumption-of-other-foods/" xr:uid="{6BDFE8F7-A4B7-4968-BA29-EAEE8DA6DABA}"/>
     <hyperlink ref="E3" r:id="rId7" display="https://history.pictures/2020/02/10/9-1-consumption-of-cereals/" xr:uid="{052EEABF-6CCA-44FB-BDE0-B029A16A356B}"/>
     <hyperlink ref="E10" r:id="rId8" display="https://history.pictures/2020/02/10/9-1-consumption-of-cereals/" xr:uid="{B6988925-7344-42C8-9532-1CBC4BBC80CF}"/>
     <hyperlink ref="E6" r:id="rId9" display="https://history.pictures/2020/10/21/9-4-consumption-of-other-foods/" xr:uid="{9505887F-FD4A-4D74-AA6F-A636530ABB6D}"/>
     <hyperlink ref="E7" r:id="rId10" display="https://history.pictures/2020/10/21/9-4-consumption-of-other-foods/" xr:uid="{2D67D00D-BEEB-4945-9941-84E709BBD8C8}"/>
-    <hyperlink ref="E12" r:id="rId11" display="https://assets.publishing.service.gov.uk/media/5a7f8e1940f0b62302690313/The_Urban_Working_-_Class_Household_Diet_1940-1949.pdf" xr:uid="{7390DD77-970B-4383-A9BE-753E26C62AE9}"/>
-    <hyperlink ref="E18" r:id="rId12" display="https://assets.publishing.service.gov.uk/media/5a7f8e1940f0b62302690313/The_Urban_Working_-_Class_Household_Diet_1940-1949.pdf" xr:uid="{215CD8F4-3FF1-44C4-AE28-9E5E36C67CCB}"/>
+    <hyperlink ref="B56" r:id="rId11" display="https://assets.publishing.service.gov.uk/media/5a7f8e1940f0b62302690313/The_Urban_Working_-_Class_Household_Diet_1940-1949.pdf" xr:uid="{7390DD77-970B-4383-A9BE-753E26C62AE9}"/>
+    <hyperlink ref="B57" r:id="rId12" display="https://dn760005.eu.archive.org/0/items/b32174755/b32174755.pdf" xr:uid="{7EC83B5C-9349-41AD-92A2-8BE9EED193C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId13"/>
@@ -2469,7 +2577,7 @@
         <v>1975</v>
       </c>
       <c r="E11">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F11">
@@ -2502,7 +2610,7 @@
         <v>2000</v>
       </c>
       <c r="E12">
-        <f>dist_calculations!E$28</f>
+        <f>dist_calculations!E$31</f>
         <v>15</v>
       </c>
       <c r="F12">
@@ -2536,7 +2644,7 @@
         <v>1997.5</v>
       </c>
       <c r="E13">
-        <f>dist_calculations!E$29</f>
+        <f>dist_calculations!E$32</f>
         <v>10</v>
       </c>
       <c r="F13">
@@ -2617,7 +2725,7 @@
         <v>32.464446038888546</v>
       </c>
       <c r="G18">
-        <f>(F18/F$32)*C$32</f>
+        <f t="shared" ref="G18:G32" si="2">(F18/F$32)*C$32</f>
         <v>32.724161607199655</v>
       </c>
       <c r="H18">
@@ -2625,7 +2733,7 @@
         <v>32.724161607199655</v>
       </c>
       <c r="I18">
-        <f t="shared" ref="I18:I32" si="2">(H18/G18 -1)*100</f>
+        <f t="shared" ref="I18:I32" si="3">(H18/G18 -1)*100</f>
         <v>0</v>
       </c>
     </row>
@@ -2649,7 +2757,7 @@
         <v>56.78286860917391</v>
       </c>
       <c r="G19">
-        <f>(F19/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>57.237131558047309</v>
       </c>
       <c r="H19">
@@ -2657,7 +2765,7 @@
         <v>53.329528968096682</v>
       </c>
       <c r="I19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-6.8270412642669083</v>
       </c>
     </row>
@@ -2681,7 +2789,7 @@
         <v>93.260502464601984</v>
       </c>
       <c r="G20">
-        <f>(F20/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>94.006586484318802</v>
       </c>
       <c r="H20">
@@ -2689,7 +2797,7 @@
         <v>94.006586484318802</v>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2710,7 +2818,7 @@
         <v>97.313572892982862</v>
       </c>
       <c r="G21">
-        <f>(F21/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>98.092081476126737</v>
       </c>
       <c r="H21">
@@ -2718,7 +2826,7 @@
         <v>94.006586484318802</v>
       </c>
       <c r="I21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-4.164959016393432</v>
       </c>
     </row>
@@ -2739,7 +2847,7 @@
         <v>107.052377231349</v>
       </c>
       <c r="G22">
-        <f>(F22/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>107.9087962491998</v>
       </c>
       <c r="H22">
@@ -2747,7 +2855,7 @@
         <v>94.006586484318802</v>
       </c>
       <c r="I22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-12.883296124234256</v>
       </c>
     </row>
@@ -2771,7 +2879,7 @@
         <v>128.45213126268297</v>
       </c>
       <c r="G23">
-        <f>(F23/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>129.47974831278447</v>
       </c>
       <c r="H23">
@@ -2779,7 +2887,7 @@
         <v>129.47974831278447</v>
       </c>
       <c r="I23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2800,7 +2908,7 @@
         <v>132.99317102493086</v>
       </c>
       <c r="G24">
-        <f>(F24/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>134.05711639313034</v>
       </c>
       <c r="H24">
@@ -2808,7 +2916,7 @@
         <v>129.47974831278447</v>
       </c>
       <c r="I24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.414490930061842</v>
       </c>
     </row>
@@ -2832,7 +2940,7 @@
         <v>99.571917962243432</v>
       </c>
       <c r="G25">
-        <f>(F25/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>100.36849330594139</v>
       </c>
       <c r="H25">
@@ -2840,7 +2948,7 @@
         <v>55.036376981453387</v>
       </c>
       <c r="I25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-45.165683803090964</v>
       </c>
     </row>
@@ -2864,7 +2972,7 @@
         <v>91.550817227198138</v>
       </c>
       <c r="G26">
-        <f>(F26/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>92.283223765015734</v>
       </c>
       <c r="H26">
@@ -2872,7 +2980,7 @@
         <v>134.80139021087473</v>
       </c>
       <c r="I26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46.073559972422082</v>
       </c>
     </row>
@@ -2885,7 +2993,7 @@
         <v>192.88</v>
       </c>
       <c r="D27">
-        <f>sources_consumption!D28</f>
+        <f>sources_consumption!D34</f>
         <v>26445.714285714286</v>
       </c>
       <c r="F27">
@@ -2893,7 +3001,7 @@
         <v>86.20341673716807</v>
       </c>
       <c r="G27">
-        <f>(F27/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>86.893044071065418</v>
       </c>
       <c r="H27">
@@ -2901,7 +3009,7 @@
         <v>134.80139021087473</v>
       </c>
       <c r="I27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>55.13484612258204</v>
       </c>
     </row>
@@ -2925,7 +3033,7 @@
         <v>88.502847280973469</v>
       </c>
       <c r="G28">
-        <f>(F28/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>89.210870059221264</v>
       </c>
       <c r="H28">
@@ -2933,7 +3041,7 @@
         <v>84.587778137920722</v>
       </c>
       <c r="I28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-5.1822069645006019</v>
       </c>
     </row>
@@ -2954,7 +3062,7 @@
         <v>90.80227782477867</v>
       </c>
       <c r="G29">
-        <f>(F29/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>91.528696047376911</v>
       </c>
       <c r="H29">
@@ -2962,7 +3070,7 @@
         <v>84.587778137920722</v>
       </c>
       <c r="I29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-7.583324366233124</v>
       </c>
     </row>
@@ -2983,7 +3091,7 @@
         <v>91.722050042300751</v>
       </c>
       <c r="G30">
-        <f>(F30/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>92.455826442639164</v>
       </c>
       <c r="H30">
@@ -2991,7 +3099,7 @@
         <v>79.765013229421356</v>
       </c>
       <c r="I30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-13.726353115334877</v>
       </c>
     </row>
@@ -3015,7 +3123,7 @@
         <v>99.080227782477962</v>
       </c>
       <c r="G31">
-        <f>(F31/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>99.872869604737787</v>
       </c>
       <c r="H31">
@@ -3023,7 +3131,7 @@
         <v>100.18191306982519</v>
       </c>
       <c r="I31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.30943685338218341</v>
       </c>
     </row>
@@ -3039,14 +3147,14 @@
         <v>100.80000000000001</v>
       </c>
       <c r="D32">
-        <f>sources_consumption!D35</f>
+        <f>sources_consumption!D41</f>
         <v>30678.266925714288</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <f>(F32/F$32)*C$32</f>
+        <f t="shared" si="2"/>
         <v>100.80000000000001</v>
       </c>
       <c r="H32">
@@ -3054,7 +3162,7 @@
         <v>100.18191306982519</v>
       </c>
       <c r="I32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.61318147834804604</v>
       </c>
     </row>
@@ -3246,7 +3354,7 @@
         <v>1982</v>
       </c>
       <c r="D6">
-        <f xml:space="preserve"> (B6+C6)/2</f>
+        <f t="shared" ref="D6:D11" si="2" xml:space="preserve"> (B6+C6)/2</f>
         <v>1966.5</v>
       </c>
       <c r="E6">
@@ -3259,7 +3367,7 @@
         <v>20</v>
       </c>
       <c r="H6">
-        <f xml:space="preserve"> E6*F6*G6/100</f>
+        <f t="shared" ref="H6:H11" si="3" xml:space="preserve"> E6*F6*G6/100</f>
         <v>12.6</v>
       </c>
       <c r="I6">
@@ -3278,11 +3386,11 @@
         <v>1990</v>
       </c>
       <c r="D7">
-        <f xml:space="preserve"> (B7+C7)/2</f>
+        <f t="shared" si="2"/>
         <v>1975.5</v>
       </c>
       <c r="E7">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F7">
@@ -3292,11 +3400,11 @@
         <v>20</v>
       </c>
       <c r="H7">
-        <f xml:space="preserve"> E7*F7*G7/100</f>
+        <f t="shared" si="3"/>
         <v>106.4</v>
       </c>
       <c r="I7">
-        <f>(G$24/C$24)*H7</f>
+        <f>(G24/C24)*H7</f>
         <v>61.284797313094742</v>
       </c>
     </row>
@@ -3311,11 +3419,11 @@
         <v>2010</v>
       </c>
       <c r="D8">
-        <f xml:space="preserve"> (B8+C8)/2</f>
+        <f t="shared" si="2"/>
         <v>1992.5</v>
       </c>
       <c r="E8">
-        <f>dist_calculations!E$26</f>
+        <f>dist_calculations!E$29</f>
         <v>11</v>
       </c>
       <c r="F8">
@@ -3325,7 +3433,7 @@
         <v>26</v>
       </c>
       <c r="H8">
-        <f xml:space="preserve"> E8*F8*G8/100</f>
+        <f t="shared" si="3"/>
         <v>22.88</v>
       </c>
       <c r="I8">
@@ -3344,7 +3452,7 @@
         <v>2010</v>
       </c>
       <c r="D9">
-        <f xml:space="preserve"> (B9+C9)/2</f>
+        <f t="shared" si="2"/>
         <v>1992.5</v>
       </c>
       <c r="E9">
@@ -3357,7 +3465,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <f xml:space="preserve"> E9*F9*G9/100</f>
+        <f t="shared" si="3"/>
         <v>57.6</v>
       </c>
       <c r="I9">
@@ -3376,11 +3484,11 @@
         <v>2010</v>
       </c>
       <c r="D10">
-        <f xml:space="preserve"> (B10+C10)/2</f>
+        <f t="shared" si="2"/>
         <v>1997.5</v>
       </c>
       <c r="E10">
-        <f>dist_calculations!E$29</f>
+        <f>dist_calculations!E$32</f>
         <v>10</v>
       </c>
       <c r="F10">
@@ -3390,7 +3498,7 @@
         <v>20</v>
       </c>
       <c r="H10">
-        <f xml:space="preserve"> E10*F10*G10/100</f>
+        <f t="shared" si="3"/>
         <v>84</v>
       </c>
       <c r="I10">
@@ -3409,11 +3517,11 @@
         <v>2010</v>
       </c>
       <c r="D11">
-        <f xml:space="preserve"> (B11+C11)/2</f>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="E11">
-        <f>dist_calculations!E$28</f>
+        <f>dist_calculations!E$31</f>
         <v>15</v>
       </c>
       <c r="F11">
@@ -3424,7 +3532,7 @@
         <v>20</v>
       </c>
       <c r="H11">
-        <f xml:space="preserve"> E11*F11*G11/100</f>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="I11">
@@ -3463,11 +3571,11 @@
         <v>109</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="11">
+      <c r="B16">
         <v>1810</v>
       </c>
       <c r="D16">
@@ -3486,15 +3594,15 @@
         <v>10.56</v>
       </c>
       <c r="E17">
-        <f>_xlfn.FORECAST.LINEAR(B17,D$16:D$23,B$16:B$23)</f>
+        <f t="shared" ref="E17:E22" si="4">_xlfn.FORECAST.LINEAR(B17,D$16:D$23,B$16:B$23)</f>
         <v>2748.2142857142899</v>
       </c>
       <c r="F17">
-        <f>(E17/D$29)*100</f>
+        <f t="shared" ref="F17:F22" si="5">(E17/D$29)*100</f>
         <v>6.4131465340996119</v>
       </c>
       <c r="G17">
-        <f>(F17/F$29)*C$29</f>
+        <f t="shared" ref="G17:G29" si="6">(F17/F$29)*C$29</f>
         <v>13.241864963608879</v>
       </c>
       <c r="H17">
@@ -3502,8 +3610,8 @@
         <v>13.241864963608879</v>
       </c>
       <c r="I17">
-        <f>(H17/C17)*100</f>
-        <v>125.39644851902348</v>
+        <f>(H17/G17)*100</f>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -3518,15 +3626,15 @@
         <v>36.96</v>
       </c>
       <c r="E18">
-        <f>_xlfn.FORECAST.LINEAR(B18,D$16:D$23,B$16:B$23)</f>
+        <f t="shared" si="4"/>
         <v>7695</v>
       </c>
       <c r="F18">
-        <f>(E18/D$29)*100</f>
+        <f t="shared" si="5"/>
         <v>17.956810295478888</v>
       </c>
       <c r="G18">
-        <f>(F18/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>37.077221898104817</v>
       </c>
       <c r="H18">
@@ -3534,8 +3642,8 @@
         <v>37.077221898104817</v>
       </c>
       <c r="I18">
-        <f>(H18/C18)*100</f>
-        <v>100.31715881521865</v>
+        <f>(H18/G18)*100</f>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -3550,15 +3658,15 @@
         <v>118.8</v>
       </c>
       <c r="E19">
-        <f>_xlfn.FORECAST.LINEAR(B19,D$16:D$23,B$16:B$23)</f>
+        <f t="shared" si="4"/>
         <v>12421.92857142858</v>
       </c>
       <c r="F19">
-        <f>(E19/D$29)*100</f>
+        <f t="shared" si="5"/>
         <v>28.987422334130219</v>
       </c>
       <c r="G19">
-        <f>(F19/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>59.853229635512079</v>
       </c>
       <c r="H19">
@@ -3566,8 +3674,8 @@
         <v>59.853229635512079</v>
       </c>
       <c r="I19">
-        <f>(H19/C19)*100</f>
-        <v>50.381506427198715</v>
+        <f>(H19/G19)*100</f>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -3579,15 +3687,15 @@
         <v>118.8</v>
       </c>
       <c r="E20">
-        <f>_xlfn.FORECAST.LINEAR(B20,D$16:D$23,B$16:B$23)</f>
+        <f t="shared" si="4"/>
         <v>13741.07142857142</v>
       </c>
       <c r="F20">
-        <f>(E20/D$29)*100</f>
+        <f t="shared" si="5"/>
         <v>32.065732670497994</v>
       </c>
       <c r="G20">
-        <f>(F20/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>66.209324818044266</v>
       </c>
       <c r="H20">
@@ -3595,8 +3703,8 @@
         <v>59.853229635512079</v>
       </c>
       <c r="I20">
-        <f>(H20/C20)*100</f>
-        <v>50.381506427198715</v>
+        <f>(H20/G20)*100</f>
+        <v>90.400000000000091</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -3611,15 +3719,15 @@
         <v>75.959999999999994</v>
       </c>
       <c r="E21">
-        <f>_xlfn.FORECAST.LINEAR(B21,D$16:D$23,B$16:B$23)</f>
+        <f t="shared" si="4"/>
         <v>16489.28571428571</v>
       </c>
       <c r="F21">
-        <f>(E21/D$29)*100</f>
+        <f t="shared" si="5"/>
         <v>38.478879204597604</v>
       </c>
       <c r="G21">
-        <f>(F21/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>79.451189781653142</v>
       </c>
       <c r="H21">
@@ -3627,8 +3735,8 @@
         <v>79.451189781653156</v>
       </c>
       <c r="I21">
-        <f>(H21/C21)*100</f>
-        <v>104.59608975994361</v>
+        <f>(H21/G21)*100</f>
+        <v>100.00000000000003</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -3643,15 +3751,15 @@
         <v>75.959999999999994</v>
       </c>
       <c r="E22">
-        <f>_xlfn.FORECAST.LINEAR(B22,D$16:D$23,B$16:B$23)</f>
+        <f t="shared" si="4"/>
         <v>16489.28571428571</v>
       </c>
       <c r="F22">
-        <f>(E22/D$29)*100</f>
+        <f t="shared" si="5"/>
         <v>38.478879204597604</v>
       </c>
       <c r="G22">
-        <f>(F22/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>79.451189781653142</v>
       </c>
       <c r="H22">
@@ -3659,8 +3767,8 @@
         <v>79.451189781653156</v>
       </c>
       <c r="I22">
-        <f>(H22/C22)*100</f>
-        <v>104.59608975994361</v>
+        <f>(H22/G22)*100</f>
+        <v>100.00000000000003</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -3672,7 +3780,7 @@
         <v>182.36</v>
       </c>
       <c r="D23">
-        <f>sources_consumption!D30</f>
+        <f>sources_consumption!D36</f>
         <v>17588.571428571431</v>
       </c>
       <c r="F23">
@@ -3680,7 +3788,7 @@
         <v>41.044137818237459</v>
       </c>
       <c r="G23">
-        <f>(F23/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>84.747935767096706</v>
       </c>
       <c r="H23">
@@ -3688,8 +3796,8 @@
         <v>74.463904622847636</v>
       </c>
       <c r="I23">
-        <f>(H23/C23)*100</f>
-        <v>40.833463820381461</v>
+        <f>(H23/G23)*100</f>
+        <v>87.865154412124539</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -3712,16 +3820,16 @@
         <v>50.870114848531436</v>
       </c>
       <c r="G24">
-        <f>(F24/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>105.03661313924772</v>
       </c>
       <c r="H24">
-        <f>I8+I9</f>
-        <v>69.408875160427726</v>
+        <f>I5+I6+I7</f>
+        <v>140.73598709474788</v>
       </c>
       <c r="I24">
-        <f>(H24/C24)*100</f>
-        <v>38.061458192820638</v>
+        <f>(H24/G24)*100</f>
+        <v>133.98755242438489</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -3741,16 +3849,16 @@
         <v>60.696091878825023</v>
       </c>
       <c r="G25">
-        <f>(F25/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>125.32529051139791</v>
       </c>
       <c r="H25">
-        <f>I8+I9</f>
-        <v>69.408875160427726</v>
+        <f>I7+I8+I9</f>
+        <v>130.69367247352247</v>
       </c>
       <c r="I25">
-        <f>(H25/C25)*100</f>
-        <v>34.794904331475699</v>
+        <f>(H25/G25)*100</f>
+        <v>104.28355836257673</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -3770,7 +3878,7 @@
         <v>64.62648269094278</v>
       </c>
       <c r="G26">
-        <f>(F26/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>133.44076146025867</v>
       </c>
       <c r="H26">
@@ -3778,8 +3886,8 @@
         <v>130.69367247352247</v>
       </c>
       <c r="I26">
-        <f>(H26/C26)*100</f>
-        <v>69.934542205437964</v>
+        <f>(H26/G26)*100</f>
+        <v>97.941341943290439</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -3802,7 +3910,7 @@
         <v>86.243632157589118</v>
       </c>
       <c r="G27">
-        <f>(F27/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>178.07585167899003</v>
       </c>
       <c r="H27">
@@ -3810,8 +3918,8 @@
         <v>192.10734687824919</v>
       </c>
       <c r="I27">
-        <f>(H27/C27)*100</f>
-        <v>93.039203253704557</v>
+        <f>(H27/G27)*100</f>
+        <v>107.87950475427357</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -3834,7 +3942,7 @@
         <v>96.069609187882705</v>
       </c>
       <c r="G28">
-        <f>(F28/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>198.36452905114024</v>
       </c>
       <c r="H28">
@@ -3842,8 +3950,8 @@
         <v>192.10734687824919</v>
       </c>
       <c r="I28">
-        <f>(H28/C28)*100</f>
-        <v>93.039203253704557</v>
+        <f>(H28/G28)*100</f>
+        <v>96.84561438336695</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -3858,14 +3966,14 @@
         <v>206.48000000000002</v>
       </c>
       <c r="D29">
-        <f>sources_consumption!D37</f>
+        <f>sources_consumption!D43</f>
         <v>42852.822262857146</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <f>(F29/F$29)*C$29</f>
+        <f t="shared" si="6"/>
         <v>206.48000000000002</v>
       </c>
       <c r="H29">
@@ -3873,7 +3981,7 @@
         <v>192.10734687824919</v>
       </c>
       <c r="I29">
-        <f>(H29/C29)*100</f>
+        <f>(H29/G29)*100</f>
         <v>93.039203253704557</v>
       </c>
     </row>
@@ -4804,7 +4912,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DD8063F-8621-472E-B7CA-29111BDF18DD}">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21.42578125" customWidth="1"/>
@@ -4819,7 +4927,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>148</v>
@@ -4892,7 +5000,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>237</v>
@@ -4906,7 +5014,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
         <v>237</v>
@@ -4920,7 +5028,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J8" t="s">
         <v>237</v>
@@ -4934,7 +5042,7 @@
         <v>12</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J9" t="s">
         <v>237</v>
@@ -4992,7 +5100,10 @@
         <v>75</v>
       </c>
       <c r="E14">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="J14" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -5003,7 +5114,10 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="J15" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -5014,10 +5128,13 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="J16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -5025,221 +5142,264 @@
         <v>4</v>
       </c>
       <c r="E17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="J17" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18">
+        <v>24</v>
+      </c>
+      <c r="E18">
+        <v>16</v>
+      </c>
+      <c r="J18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>30</v>
+      </c>
+      <c r="E19">
+        <v>24</v>
+      </c>
+      <c r="J19" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>27</v>
+      </c>
+      <c r="E20">
+        <v>28</v>
+      </c>
+      <c r="J20" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>12</v>
+      </c>
+      <c r="E21">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>174</v>
       </c>
-      <c r="C19">
+      <c r="C22">
         <v>1</v>
       </c>
-      <c r="D19">
+      <c r="D22">
         <f>sources_distweight!H8</f>
         <v>14.90233829609822</v>
       </c>
-      <c r="E19">
-        <f>MAX(ROUND((D19/D$30)*(C$30/C19)*E$30,0),1)</f>
+      <c r="E22">
+        <f>MAX(ROUND((D22/D$33)*(C$33/C22)*E$33,0),1)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>58</v>
       </c>
-      <c r="C20">
+      <c r="C23">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25">
         <v>1</v>
       </c>
-      <c r="D21">
-        <f>sources_distweight!H15</f>
-        <v>0.29385028798945501</v>
-      </c>
-      <c r="E21">
-        <f>MAX(ROUND((D21/D$30)*(C$30/C21)*E$30,0),1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
+      <c r="D25">
         <f>sources_distweight!H12</f>
         <v>4.1600596661821294</v>
       </c>
-      <c r="E22">
-        <f>MAX(ROUND((D22/D$30)*(C$30/C22)*E$30,0),1)</f>
+      <c r="E25">
+        <f t="shared" ref="E25:E32" si="0">MAX(ROUND((D25/D$33)*(C$33/C25)*E$33,0),1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>144</v>
       </c>
-      <c r="C23">
+      <c r="C26">
         <v>1</v>
       </c>
-      <c r="D23">
+      <c r="D26">
         <f>sources_distweight!H25</f>
         <v>1.5810912357314428</v>
       </c>
-      <c r="E23">
-        <f>MAX(ROUND((D23/D$30)*(C$30/C23)*E$30,0),1)</f>
+      <c r="E26">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="C24">
+      <c r="C27">
         <v>4</v>
       </c>
-      <c r="D24">
+      <c r="D27">
         <f>sources_distweight!H21</f>
         <v>82.687198110902756</v>
       </c>
-      <c r="E24">
-        <f>MAX(ROUND((D24/D$30)*(C$30/C24)*E$30,0),1)</f>
+      <c r="E27">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="G24">
+      <c r="G27">
         <v>8.3333300000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>146</v>
       </c>
-      <c r="C25">
+      <c r="C28">
         <v>1</v>
       </c>
-      <c r="D25">
+      <c r="D28">
         <f>sources_distweight!H27</f>
         <v>36.686608891001427</v>
       </c>
-      <c r="E25">
-        <f>MAX(ROUND((D25/D$30)*(C$30/C25)*E$30,0),1)</f>
+      <c r="E28">
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>156</v>
       </c>
-      <c r="C26">
+      <c r="C29">
         <v>1</v>
       </c>
-      <c r="D26">
+      <c r="D29">
         <f>sources_distweight!H26</f>
         <v>5.8367306681692117</v>
       </c>
-      <c r="E26">
-        <f>MAX(ROUND((D26/D$30)*(C$30/C26)*E$30,0),1)</f>
+      <c r="E29">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>145</v>
       </c>
-      <c r="C27">
+      <c r="C30">
         <v>1</v>
       </c>
-      <c r="D27">
+      <c r="D30">
         <f>sources_distweight!H33</f>
         <v>9.3171730705664011</v>
       </c>
-      <c r="E27">
-        <f>MAX(ROUND((D27/D$30)*(C$30/C27)*E$30,0),1)</f>
+      <c r="E30">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>151</v>
       </c>
-      <c r="C28">
+      <c r="C31">
         <v>4</v>
       </c>
-      <c r="D28">
+      <c r="D31">
         <f>sources_distweight!H31 *(50/150)</f>
         <v>33.333333333333329</v>
       </c>
-      <c r="E28">
-        <f>MAX(ROUND((D28/D$30)*(C$30/C28)*E$30,0),1)</f>
+      <c r="E31">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="F28">
+      <c r="F31">
         <v>23800</v>
       </c>
-      <c r="G28">
+      <c r="G31">
         <f>(25/12)*4</f>
         <v>8.3333333333333339</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
-      <c r="C29">
+      <c r="C32">
         <v>12</v>
       </c>
-      <c r="D29">
+      <c r="D32">
         <f>sources_distweight!H31 *(100/150)</f>
         <v>66.666666666666657</v>
       </c>
-      <c r="E29">
-        <f>MAX(ROUND((D29/D$30)*(C$30/C29)*E$30,0),1)</f>
+      <c r="E32">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F29">
+      <c r="F32">
         <v>23800</v>
       </c>
-      <c r="G29">
+      <c r="G32">
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>147</v>
       </c>
-      <c r="C30">
+      <c r="C33">
         <v>1</v>
       </c>
-      <c r="D30">
+      <c r="D33">
         <f>sources_distweight!H34</f>
         <v>54.857878770717939</v>
       </c>
-      <c r="E30">
+      <c r="E33">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>150</v>
       </c>
-      <c r="C31">
+      <c r="C34">
         <v>6</v>
       </c>
-      <c r="D31">
+      <c r="D34">
         <f>sources_distweight!H37</f>
         <v>151.79897460247545</v>
       </c>
-      <c r="E31">
-        <f>MAX(ROUND((D31/D$30)*(C$30/C31)*E$30,0),1)</f>
+      <c r="E34">
+        <f>MAX(ROUND((D34/D$33)*(C$33/C34)*E$33,0),1)</f>
         <v>46</v>
       </c>
     </row>
@@ -5359,7 +5519,7 @@
       </c>
       <c r="B3">
         <f>SUMPRODUCT(S3:X3,G38:L38)/SUM(G38:L38)</f>
-        <v>1.6790785790484388</v>
+        <v>0.76778272577101325</v>
       </c>
       <c r="C3" s="8">
         <f>meat!H2</f>
@@ -5379,11 +5539,11 @@
       </c>
       <c r="K3" s="8">
         <f>meat!I2</f>
-        <v>72</v>
+        <v>55.29161825631887</v>
       </c>
       <c r="M3">
         <f>fish!I2</f>
-        <v>197.66064034529006</v>
+        <v>28.464668020376386</v>
       </c>
       <c r="O3">
         <f>vegetables!I2</f>
@@ -5395,11 +5555,12 @@
       </c>
       <c r="S3" s="8">
         <f>K3/C3</f>
-        <v>1.5</v>
-      </c>
-      <c r="U3">
+        <v>1.1519087136733097</v>
+      </c>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11">
         <f>M3/E3</f>
-        <v>13.177376023019338</v>
+        <v>1.8976445346917592</v>
       </c>
       <c r="W3">
         <f>O3/G3</f>
@@ -5429,10 +5590,11 @@
         <v>48.818825999999994</v>
       </c>
       <c r="S4" s="8"/>
-      <c r="T4" s="8">
+      <c r="T4" s="11">
         <f>L4/D4</f>
         <v>0.23247059999999997</v>
       </c>
+      <c r="U4" s="11"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -5453,6 +5615,8 @@
         <v>13.241864963608879</v>
       </c>
       <c r="S5" s="8"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
       <c r="Y5">
         <f>Q5/I5</f>
         <v>1.2539644851902347</v>
@@ -5464,7 +5628,7 @@
       </c>
       <c r="B6">
         <f>SUMPRODUCT(S6:Z6,G41:N41)/SUM(G41:N41)</f>
-        <v>4.4903526176632491</v>
+        <v>1.8976445346917592</v>
       </c>
       <c r="C6" s="8"/>
       <c r="E6">
@@ -5474,12 +5638,13 @@
       <c r="K6" s="8"/>
       <c r="M6">
         <f>fish!I3</f>
-        <v>242.47904135381546</v>
+        <v>102.472804873355</v>
       </c>
       <c r="S6" s="8"/>
-      <c r="U6" s="8">
+      <c r="T6" s="11"/>
+      <c r="U6" s="11">
         <f>M6/E6</f>
-        <v>4.4903526176632491</v>
+        <v>1.8976445346917592</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -5488,7 +5653,7 @@
       </c>
       <c r="B7">
         <f>SUMPRODUCT(S7:X7,G42:L42)/SUM(G42:L42)</f>
-        <v>0.82047562332820978</v>
+        <v>1.0411368116592619</v>
       </c>
       <c r="C7" s="8"/>
       <c r="G7">
@@ -5502,16 +5667,18 @@
       <c r="K7" s="8"/>
       <c r="O7">
         <f>vegetables!I3</f>
-        <v>23.700316298826298</v>
+        <v>35.616020468703105</v>
       </c>
       <c r="P7">
         <f>fruit!I3</f>
         <v>20.605367360897031</v>
       </c>
       <c r="S7" s="8"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
       <c r="W7">
         <f>O7/G7</f>
-        <v>0.8777894925491222</v>
+        <v>1.319111869211226</v>
       </c>
       <c r="X7">
         <f>P7/H7</f>
@@ -5537,6 +5704,8 @@
         <v>107.280936523349</v>
       </c>
       <c r="S8" s="8"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
       <c r="V8">
         <f>N8/F8</f>
         <v>3.3525292663546562</v>
@@ -5548,7 +5717,7 @@
       </c>
       <c r="B9">
         <f>AVERAGE(S9:V9)</f>
-        <v>0.625</v>
+        <v>1.1519087136733097</v>
       </c>
       <c r="C9" s="8">
         <f>meat!H3</f>
@@ -5556,12 +5725,14 @@
       </c>
       <c r="K9" s="8">
         <f>meat!I3</f>
-        <v>15</v>
+        <v>27.645809128159435</v>
       </c>
       <c r="S9" s="8">
         <f>K9/C9</f>
-        <v>0.625</v>
-      </c>
+        <v>1.1519087136733097</v>
+      </c>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -5569,7 +5740,7 @@
       </c>
       <c r="B10">
         <f>SUMPRODUCT(S10:X10,G45:L45)/SUM(G45:L45)</f>
-        <v>1.0585945486012034</v>
+        <v>0.99527650738650753</v>
       </c>
       <c r="C10" s="8">
         <f>meat!H4</f>
@@ -5589,11 +5760,11 @@
       </c>
       <c r="K10" s="8">
         <f>meat!I4</f>
-        <v>54</v>
+        <v>50.928693373621392</v>
       </c>
       <c r="M10">
         <f>fish!I4</f>
-        <v>36.436075631365064</v>
+        <v>24.007125768386146</v>
       </c>
       <c r="O10">
         <f>vegetables!I4</f>
@@ -5605,11 +5776,12 @@
       </c>
       <c r="S10" s="8">
         <f>K10/C10</f>
-        <v>0.9375</v>
-      </c>
-      <c r="U10">
+        <v>0.88417870440314916</v>
+      </c>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11">
         <f>M10/E10</f>
-        <v>2.0242264239647256</v>
+        <v>1.3337292093547859</v>
       </c>
       <c r="W10">
         <f>O10/G10</f>
@@ -5639,10 +5811,11 @@
         <v>88.6875374318181</v>
       </c>
       <c r="S11" s="8"/>
-      <c r="T11" s="8">
+      <c r="T11" s="11">
         <f>L11/D11</f>
         <v>0.42232160681818143</v>
       </c>
+      <c r="U11" s="11"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -5663,6 +5836,8 @@
         <v>37.077221898104817</v>
       </c>
       <c r="S12" s="8"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
       <c r="Y12">
         <f>Q12/I12</f>
         <v>1.0031715881521865</v>
@@ -5674,7 +5849,7 @@
       </c>
       <c r="B13">
         <f>SUMPRODUCT(S13:Z13,G48:N48)/SUM(G48:N48)</f>
-        <v>2.0242264239647256</v>
+        <v>1.3337292093547859</v>
       </c>
       <c r="C13" s="8"/>
       <c r="E13">
@@ -5684,12 +5859,13 @@
       <c r="K13" s="8"/>
       <c r="M13">
         <f>fish!I5</f>
-        <v>273.27056723523793</v>
+        <v>180.05344326289611</v>
       </c>
       <c r="S13" s="8"/>
-      <c r="U13" s="8">
+      <c r="T13" s="11"/>
+      <c r="U13" s="11">
         <f>M13/E13</f>
-        <v>2.0242264239647256</v>
+        <v>1.3337292093547859</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
@@ -5719,6 +5895,8 @@
         <v>52.225881380177114</v>
       </c>
       <c r="S14" s="8"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
       <c r="W14">
         <f>O14/G14</f>
         <v>1.1373401860400343</v>
@@ -5747,6 +5925,8 @@
         <v>90.518290191575701</v>
       </c>
       <c r="S15" s="8"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
       <c r="V15">
         <f>N15/F15</f>
         <v>1.508638169859595</v>
@@ -5758,7 +5938,7 @@
       </c>
       <c r="B16">
         <f>AVERAGE(S16:V16)</f>
-        <v>0.93333333333333335</v>
+        <v>0.88417870440314916</v>
       </c>
       <c r="C16" s="8">
         <f>meat!H5</f>
@@ -5766,12 +5946,14 @@
       </c>
       <c r="K16" s="8">
         <f>meat!I5</f>
-        <v>56</v>
+        <v>53.050722264188948</v>
       </c>
       <c r="S16" s="8">
         <f>K16/C16</f>
-        <v>0.93333333333333335</v>
-      </c>
+        <v>0.88417870440314916</v>
+      </c>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -5779,7 +5961,7 @@
       </c>
       <c r="B17">
         <f>SUMPRODUCT(S17:X17,G52:L52)/SUM(G52:L52)</f>
-        <v>1.8132189177282256</v>
+        <v>1.7142774862635335</v>
       </c>
       <c r="C17" s="8">
         <f>meat!H6</f>
@@ -5799,11 +5981,11 @@
       </c>
       <c r="K17" s="8">
         <f>meat!I6</f>
-        <v>16.873956940808974</v>
+        <v>13.381047854061519</v>
       </c>
       <c r="M17">
         <f>fish!I6</f>
-        <v>7.2688937940497906</v>
+        <v>5.3793890091180065</v>
       </c>
       <c r="O17">
         <f>vegetables!I6</f>
@@ -5815,11 +5997,12 @@
       </c>
       <c r="S17" s="8">
         <f>K17/C17</f>
-        <v>1.3182778860007009</v>
-      </c>
-      <c r="U17">
+        <v>1.0453943635985561</v>
+      </c>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11">
         <f>M17/E17</f>
-        <v>1.8172234485124477</v>
+        <v>1.3448472522795016</v>
       </c>
       <c r="W17">
         <f>O17/G17</f>
@@ -5849,10 +6032,11 @@
         <v>156.03427587272731</v>
       </c>
       <c r="S18" s="8"/>
-      <c r="T18" s="8">
+      <c r="T18" s="11">
         <f>L18/D18</f>
         <v>0.69348567054545474</v>
       </c>
+      <c r="U18" s="11"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -5873,6 +6057,8 @@
         <v>59.853229635512079</v>
       </c>
       <c r="S19" s="8"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
       <c r="Y19">
         <f>Q19/I19</f>
         <v>0.50381506427198719</v>
@@ -5883,8 +6069,8 @@
         <v>51</v>
       </c>
       <c r="B20">
-        <f>SUMPRODUCT(S20:Z20,G55:N55)/SUM(G55:N55)</f>
-        <v>1.8172234485124477</v>
+        <f t="shared" ref="B20:B26" si="0">SUMPRODUCT(S20:Z20,G55:N55)/SUM(G55:N55)</f>
+        <v>1.3448472522795014</v>
       </c>
       <c r="C20" s="8"/>
       <c r="E20">
@@ -5894,12 +6080,13 @@
       <c r="K20" s="8"/>
       <c r="M20">
         <f>fish!I7</f>
-        <v>381.61692418761402</v>
+        <v>282.41792297869534</v>
       </c>
       <c r="S20" s="8"/>
-      <c r="U20" s="8">
+      <c r="T20" s="11"/>
+      <c r="U20" s="11">
         <f>M20/E20</f>
-        <v>1.8172234485124477</v>
+        <v>1.3448472522795016</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
@@ -5907,7 +6094,7 @@
         <v>61</v>
       </c>
       <c r="B21">
-        <f>SUMPRODUCT(S21:Z21,G56:N56)/SUM(G56:N56)</f>
+        <f t="shared" si="0"/>
         <v>1.5870886220955533</v>
       </c>
       <c r="C21" s="8"/>
@@ -5929,6 +6116,8 @@
         <v>116.99977257179319</v>
       </c>
       <c r="S21" s="8"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
       <c r="W21">
         <f>O21/G21</f>
         <v>2.5006565584098968</v>
@@ -5943,7 +6132,7 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <f>SUMPRODUCT(S22:Z22,G57:N57)/SUM(G57:N57)</f>
+        <f t="shared" si="0"/>
         <v>0.65481735652773088</v>
       </c>
       <c r="C22" s="8"/>
@@ -5957,6 +6146,8 @@
         <v>53.040205878746193</v>
       </c>
       <c r="S22" s="8"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
       <c r="V22">
         <f>N22/F22</f>
         <v>0.65481735652773077</v>
@@ -5967,8 +6158,8 @@
         <v>24</v>
       </c>
       <c r="B23">
-        <f>SUMPRODUCT(S23:Z23,G58:N58)/SUM(G58:N58)</f>
-        <v>1.3182778860007012</v>
+        <f t="shared" si="0"/>
+        <v>1.0453943635985561</v>
       </c>
       <c r="C23" s="8">
         <f>meat!H7</f>
@@ -5976,20 +6167,22 @@
       </c>
       <c r="K23" s="8">
         <f>meat!I7</f>
-        <v>106.78050876605678</v>
+        <v>84.676943451483041</v>
       </c>
       <c r="S23" s="8">
         <f>K23/C23</f>
-        <v>1.3182778860007009</v>
-      </c>
+        <v>1.0453943635985561</v>
+      </c>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <f>SUMPRODUCT(S24:Z24,G59:N59)/SUM(G59:N59)</f>
-        <v>1.8680266506940957</v>
+        <f t="shared" si="0"/>
+        <v>1.8309629729349342</v>
       </c>
       <c r="C24" s="8">
         <f>meat!H8</f>
@@ -6009,11 +6202,11 @@
       </c>
       <c r="K24" s="8">
         <f>meat!I8</f>
-        <v>13.498277739832433</v>
+        <v>12.624045463478957</v>
       </c>
       <c r="M24">
         <f>fish!I8</f>
-        <v>2.8810030043836643</v>
+        <v>2.5454768386781073</v>
       </c>
       <c r="O24">
         <f>vegetables!I8</f>
@@ -6025,11 +6218,12 @@
       </c>
       <c r="S24" s="8">
         <f>K24/C24</f>
-        <v>1.7575882473740148</v>
-      </c>
-      <c r="U24">
+        <v>1.6437559197238225</v>
+      </c>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11">
         <f>M24/E24</f>
-        <v>1.2004179184931936</v>
+        <v>1.0606153494492114</v>
       </c>
       <c r="W24">
         <f>O24/G24</f>
@@ -6045,7 +6239,7 @@
         <v>155</v>
       </c>
       <c r="B25">
-        <f>SUMPRODUCT(S25:Z25,G60:N60)/SUM(G60:N60)</f>
+        <f t="shared" si="0"/>
         <v>1.0459608975994359</v>
       </c>
       <c r="C25" s="8"/>
@@ -6059,6 +6253,8 @@
         <v>66.272082471900262</v>
       </c>
       <c r="S25" s="8"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
       <c r="Y25">
         <f>Q25/I25</f>
         <v>1.0459608975994359</v>
@@ -6069,7 +6265,7 @@
         <v>52</v>
       </c>
       <c r="B26">
-        <f>SUMPRODUCT(S26:Z26,G61:N61)/SUM(G61:N61)</f>
+        <f t="shared" si="0"/>
         <v>0.9569443712992397</v>
       </c>
       <c r="C26" s="8"/>
@@ -6083,7 +6279,8 @@
         <v>172.24998683386315</v>
       </c>
       <c r="S26" s="8"/>
-      <c r="U26" s="8">
+      <c r="T26" s="11"/>
+      <c r="U26" s="11">
         <f>M26/E26</f>
         <v>0.9569443712992397</v>
       </c>
@@ -6154,7 +6351,7 @@
       </c>
       <c r="B29">
         <f>AVERAGE(S29:V29)</f>
-        <v>1.7575882473740148</v>
+        <v>1.6437559197238223</v>
       </c>
       <c r="C29" s="8">
         <f>meat!H9</f>
@@ -6162,11 +6359,11 @@
       </c>
       <c r="K29" s="8">
         <f>meat!I9</f>
-        <v>84.364235873952708</v>
+        <v>78.900284146743473</v>
       </c>
       <c r="S29" s="8">
         <f>K29/C29</f>
-        <v>1.7575882473740148</v>
+        <v>1.6437559197238223</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
@@ -6175,7 +6372,7 @@
       </c>
       <c r="B30">
         <f>SUMPRODUCT(S30:Z30,G65:N65)/SUM(G65:N65)</f>
-        <v>1.0265978033627234</v>
+        <v>1.0228644316873223</v>
       </c>
       <c r="C30" s="8">
         <f>meat!H10</f>
@@ -6207,7 +6404,7 @@
       </c>
       <c r="K30" s="8">
         <f>meat!I10</f>
-        <v>7.4279381204819153</v>
+        <v>7.3453667003720486</v>
       </c>
       <c r="L30">
         <f>milk!I5</f>
@@ -6215,7 +6412,7 @@
       </c>
       <c r="M30">
         <f>fish!I10</f>
-        <v>3.2657654825778981</v>
+        <v>3.089614245582486</v>
       </c>
       <c r="N30">
         <f>flour!I6</f>
@@ -6235,30 +6432,30 @@
       </c>
       <c r="S30" s="8">
         <f>K30/C30</f>
-        <v>0.73689862306368203</v>
-      </c>
-      <c r="T30" s="8">
-        <f>L30/D30</f>
+        <v>0.72870701392579851</v>
+      </c>
+      <c r="T30" s="11">
+        <f t="shared" ref="T30:Y31" si="1">L30/D30</f>
         <v>2.6393789786452633</v>
       </c>
-      <c r="U30" s="8">
-        <f>M30/E30</f>
-        <v>1.0367509468501264</v>
-      </c>
-      <c r="V30">
-        <f>N30/F30</f>
+      <c r="U30" s="11">
+        <f t="shared" si="1"/>
+        <v>0.98082991923253526</v>
+      </c>
+      <c r="V30" s="11">
+        <f t="shared" si="1"/>
         <v>0.35214643932482109</v>
       </c>
-      <c r="W30">
-        <f>O30/G30</f>
+      <c r="W30" s="11">
+        <f t="shared" si="1"/>
         <v>0.89060477756663237</v>
       </c>
-      <c r="X30">
-        <f>P30/H30</f>
+      <c r="X30" s="11">
+        <f t="shared" si="1"/>
         <v>0.47844889965271536</v>
       </c>
-      <c r="Y30">
-        <f>Q30/I30</f>
+      <c r="Y30" s="11">
+        <f t="shared" si="1"/>
         <v>1.0459608975994359</v>
       </c>
     </row>
@@ -6268,7 +6465,7 @@
       </c>
       <c r="B31">
         <f>SUMPRODUCT(S31:Z31,G66:N66)/SUM(G66:N66)</f>
-        <v>1.238815254062577</v>
+        <v>1.2275923866823297</v>
       </c>
       <c r="C31" s="8">
         <f>meat!H11</f>
@@ -6300,7 +6497,7 @@
       </c>
       <c r="K31" s="8">
         <f>meat!I11</f>
-        <v>97.863608655259725</v>
+        <v>91.295986664338812</v>
       </c>
       <c r="L31">
         <f>milk!I6</f>
@@ -6328,30 +6525,30 @@
       </c>
       <c r="S31" s="8">
         <f>K31/C31</f>
-        <v>1.149713447547694</v>
-      </c>
-      <c r="T31" s="8">
-        <f>L31/D31</f>
+        <v>1.0725562343084916</v>
+      </c>
+      <c r="T31" s="11">
+        <f t="shared" si="1"/>
         <v>2.924316436730277</v>
       </c>
-      <c r="U31" s="8">
-        <f>M31/E31</f>
+      <c r="U31" s="11">
+        <f t="shared" si="1"/>
         <v>0.94993543114105283</v>
       </c>
-      <c r="V31">
-        <f>N31/F31</f>
+      <c r="V31" s="11">
+        <f t="shared" si="1"/>
         <v>1.0595168248172218</v>
       </c>
-      <c r="W31">
-        <f>O31/G31</f>
+      <c r="W31" s="11">
+        <f t="shared" si="1"/>
         <v>1.1998354398459878</v>
       </c>
-      <c r="X31">
-        <f>P31/H31</f>
+      <c r="X31" s="11">
+        <f t="shared" si="1"/>
         <v>0.93708897121030721</v>
       </c>
-      <c r="Y31">
-        <f>Q31/I31</f>
+      <c r="Y31" s="11">
+        <f t="shared" si="1"/>
         <v>0.57598493715314603</v>
       </c>
     </row>
@@ -6363,6 +6560,7 @@
         <f>SUMPRODUCT(S32:Z32,G67:N67)/SUM(G67:N67)</f>
         <v>0.94852260882128114</v>
       </c>
+      <c r="C32" s="8"/>
       <c r="D32">
         <f>milk!H7</f>
         <v>2.88</v>
@@ -6371,6 +6569,7 @@
         <f>canned!H8</f>
         <v>22.88</v>
       </c>
+      <c r="K32" s="8"/>
       <c r="L32">
         <f>milk!I7</f>
         <v>3.0898640683461114</v>
@@ -6379,11 +6578,16 @@
         <f>canned!I8</f>
         <v>19.732543037656392</v>
       </c>
-      <c r="T32">
+      <c r="S32" s="8"/>
+      <c r="T32" s="11">
         <f>L32/D32</f>
         <v>1.0728694681757331</v>
       </c>
-      <c r="Y32">
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11">
         <f>Q32/I32</f>
         <v>0.86243632157589123</v>
       </c>
@@ -6396,7 +6600,7 @@
         <f>SUMPRODUCT(S33:Z33,G68:N68)/SUM(G68:N68)</f>
         <v>1</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="8">
         <f>meat!H12</f>
         <v>33.6</v>
       </c>
@@ -6456,27 +6660,27 @@
         <f>K33/C33</f>
         <v>1</v>
       </c>
-      <c r="T33" s="8">
+      <c r="T33" s="11">
         <f>L33/D33</f>
         <v>1</v>
       </c>
-      <c r="U33" s="8">
-        <f>M33/E33</f>
+      <c r="U33" s="11">
+        <f t="shared" ref="U33:X34" si="2">M33/E33</f>
         <v>1</v>
       </c>
-      <c r="V33">
-        <f>N33/F33</f>
+      <c r="V33" s="11">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="W33">
-        <f>O33/G33</f>
+      <c r="W33" s="11">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="X33">
-        <f>P33/H33</f>
+      <c r="X33" s="11">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="11">
         <f>Q33/I33</f>
         <v>1</v>
       </c>
@@ -6549,27 +6753,27 @@
         <f>K34/C34</f>
         <v>1.0068672382591595</v>
       </c>
-      <c r="T34" s="8">
+      <c r="T34" s="11">
         <f>L34/D34</f>
         <v>1.0225964260977103</v>
       </c>
-      <c r="U34" s="8">
-        <f>M34/E34</f>
+      <c r="U34" s="11">
+        <f t="shared" si="2"/>
         <v>0.99536603562433523</v>
       </c>
-      <c r="V34">
-        <f>N34/F34</f>
+      <c r="V34" s="11">
+        <f t="shared" si="2"/>
         <v>1.0000523823195235</v>
       </c>
-      <c r="W34">
-        <f>O34/G34</f>
+      <c r="W34" s="11">
+        <f t="shared" si="2"/>
         <v>1.0106542332328086</v>
       </c>
-      <c r="X34">
-        <f>P34/H34</f>
+      <c r="X34" s="11">
+        <f t="shared" si="2"/>
         <v>0.99080227782477936</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="11">
         <f>Q34/I34</f>
         <v>0.9606960918788271</v>
       </c>
@@ -6656,14 +6860,14 @@
       </c>
       <c r="C38">
         <f>dist_calculations!E14</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
       <c r="E38">
-        <f>ROUND((D38*B3)/(C38/B38),0)</f>
-        <v>10</v>
+        <f t="shared" ref="E38:E43" si="3">ROUND((D38*B3)/(C38/B38),0)</f>
+        <v>4</v>
       </c>
       <c r="G38" s="8">
         <v>16</v>
@@ -6678,20 +6882,20 @@
         <v>16</v>
       </c>
       <c r="O38" s="8">
-        <f>ROUND((S3/($E38/$D38))*G38,0)</f>
-        <v>10</v>
+        <f>ROUND((S3/(($E38/$D38)*($C38/$B38)))*G38,0)</f>
+        <v>27</v>
       </c>
       <c r="Q38">
-        <f>ROUND((U3/($E38/$D38))*I38,0)</f>
-        <v>26</v>
+        <f>ROUND((U3/(($E38/$D38)*($C38/$B38)))*I38,0)</f>
+        <v>14</v>
       </c>
       <c r="S38">
-        <f>ROUND((W3/($E38/$D38))*K38,0)</f>
-        <v>5</v>
+        <f>ROUND((W3/(($E38/$D38)*($C38/$B38)))*K38,0)</f>
+        <v>19</v>
       </c>
       <c r="T38">
-        <f>ROUND((X3/($E38/$D38))*L38,0)</f>
-        <v>4</v>
+        <f>ROUND((X3/(($E38/$D38)*($C38/$B38)))*L38,0)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
@@ -6708,12 +6912,14 @@
         <v>5</v>
       </c>
       <c r="E39">
-        <f>ROUND((D39*B4)/(C39/B39),0)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
+      <c r="G39" s="8"/>
       <c r="H39">
         <v>100</v>
       </c>
+      <c r="O39" s="8"/>
       <c r="P39">
         <f>ROUND((T4/(($E39/$D39)*($C39/$B39)))*H39,0)</f>
         <v>102</v>
@@ -6734,12 +6940,14 @@
         <v>4</v>
       </c>
       <c r="E40">
-        <f>ROUND((D40*B5)/(C40/B40),0)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
+      <c r="G40" s="8"/>
       <c r="M40">
         <v>33</v>
       </c>
+      <c r="O40" s="8"/>
       <c r="U40">
         <f>ROUND((Y5/(($E40/$D40)*($C40/$B40)))*M40,0)</f>
         <v>33</v>
@@ -6754,21 +6962,23 @@
       </c>
       <c r="C41">
         <f>dist_calculations!E6</f>
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
       <c r="E41">
-        <f>ROUND((D41*B6)/(C41/B41),0)</f>
-        <v>4</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="G41" s="8"/>
       <c r="I41">
         <v>100</v>
       </c>
+      <c r="O41" s="8"/>
       <c r="Q41">
         <f>ROUND((U6/(($E41/$D41)*($C41/$B41)))*I41,0)</f>
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
@@ -6786,8 +6996,8 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <f>ROUND((D42*B7)/(C42/B42),0)</f>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="G42" s="8"/>
       <c r="K42">
@@ -6799,11 +7009,11 @@
       <c r="O42" s="8"/>
       <c r="S42">
         <f>ROUND((W7/(($E42/$D42)*($C42/$B42)))*K42,0)</f>
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="T42">
         <f>ROUND((X7/(($E42/$D42)*($C42/$B42)))*L42,0)</f>
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
@@ -6820,7 +7030,7 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <f>ROUND((D43*B8)/(C43/B43),0)</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="G43" s="8"/>
@@ -6840,19 +7050,23 @@
       <c r="B44">
         <v>24</v>
       </c>
+      <c r="C44">
+        <f>dist_calculations!E18</f>
+        <v>16</v>
+      </c>
       <c r="D44">
         <v>1</v>
       </c>
       <c r="E44">
-        <f>ROUND(D44*B9,0)</f>
-        <v>1</v>
+        <f>ROUND((D44*B9)/(C44/B44),0)</f>
+        <v>2</v>
       </c>
       <c r="G44" s="8">
         <v>100</v>
       </c>
       <c r="O44" s="8">
-        <f>ROUND((S9/($E44/$D44))*G44,0)</f>
-        <v>63</v>
+        <f>ROUND((S9/(($E44/$D44)*($C44/$B44)))*G44,0)</f>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
@@ -6864,14 +7078,14 @@
       </c>
       <c r="C45">
         <f>dist_calculations!E15</f>
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D45">
         <v>8</v>
       </c>
       <c r="E45">
         <f>ROUND((D45*B10)/(C45/B45),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G45" s="8">
         <v>16</v>
@@ -6886,19 +7100,19 @@
         <v>16</v>
       </c>
       <c r="O45" s="8">
-        <f>ROUND((S10/($E45/$D45))*G45,0)</f>
-        <v>15</v>
+        <f>ROUND((S10/(($E45/$D45)*($C45/$B45)))*G45,0)</f>
+        <v>14</v>
       </c>
       <c r="Q45">
-        <f>ROUND((U10/($E45/$D45))*I45,0)</f>
-        <v>10</v>
+        <f>ROUND((U10/(($E45/$D45)*($C45/$B45)))*I45,0)</f>
+        <v>7</v>
       </c>
       <c r="S45">
-        <f>ROUND((W10/($E45/$D45))*K45,0)</f>
+        <f>ROUND((W10/(($E45/$D45)*($C45/$B45)))*K45,0)</f>
         <v>35</v>
       </c>
       <c r="T45">
-        <f>ROUND((X10/($E45/$D45))*L45,0)</f>
+        <f>ROUND((X10/(($E45/$D45)*($C45/$B45)))*L45,0)</f>
         <v>12</v>
       </c>
     </row>
@@ -6920,9 +7134,11 @@
         <f>ROUND((D46*B12)/(C46/B46),0)</f>
         <v>7</v>
       </c>
+      <c r="G46" s="8"/>
       <c r="M46">
         <v>33</v>
       </c>
+      <c r="O46" s="8"/>
       <c r="U46">
         <f>ROUND((Y12/(($E46/$D46)*($C46/$B46)))*M46,0)</f>
         <v>33</v>
@@ -6945,9 +7161,11 @@
         <f>ROUND((D47*B11)/(C47/B47),0)</f>
         <v>7</v>
       </c>
+      <c r="G47" s="8"/>
       <c r="H47">
         <v>100</v>
       </c>
+      <c r="O47" s="8"/>
       <c r="P47">
         <f>ROUND((T11/(($E47/$D47)*($C47/$B47)))*H47,0)</f>
         <v>106</v>
@@ -6962,21 +7180,23 @@
       </c>
       <c r="C48">
         <f>dist_calculations!E7</f>
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D48">
         <v>5</v>
       </c>
       <c r="E48">
         <f>ROUND((D48*B13)/(C48/B48),0)</f>
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G48" s="8"/>
       <c r="I48">
         <v>100</v>
       </c>
+      <c r="O48" s="8"/>
       <c r="Q48">
         <f>ROUND((U13/(($E48/$D48)*($C48/$B48)))*I48,0)</f>
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -7048,19 +7268,23 @@
       <c r="B51">
         <v>30</v>
       </c>
+      <c r="C51">
+        <f>dist_calculations!E19</f>
+        <v>24</v>
+      </c>
       <c r="D51">
         <v>2</v>
       </c>
       <c r="E51">
-        <f>ROUND(D51*B16,0)</f>
+        <f>ROUND((D51*B16)/(C51/B51),0)</f>
         <v>2</v>
       </c>
       <c r="G51" s="8">
         <v>100</v>
       </c>
       <c r="O51" s="8">
-        <f>ROUND((S16/($E51/$D51))*G51,0)</f>
-        <v>93</v>
+        <f>ROUND((S16/(($E51/$D51)*($C51/$B51)))*G51,0)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -7072,14 +7296,14 @@
       </c>
       <c r="C52">
         <f>dist_calculations!E16</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D52">
         <v>8</v>
       </c>
       <c r="E52">
         <f>ROUND((D52*B17)/(C52/B52),0)</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G52" s="8">
         <v>16</v>
@@ -7094,20 +7318,20 @@
         <v>16</v>
       </c>
       <c r="O52" s="8">
-        <f>ROUND((S17/($E52/$D52))*G52,0)</f>
-        <v>17</v>
+        <f>ROUND((S17/(($E52/$D52)*($C52/$B52)))*G52,0)</f>
+        <v>10</v>
       </c>
       <c r="Q52">
-        <f>ROUND((U17/($E52/$D52))*I52,0)</f>
-        <v>7</v>
+        <f>ROUND((U17/(($E52/$D52)*($C52/$B52)))*I52,0)</f>
+        <v>4</v>
       </c>
       <c r="S52">
-        <f>ROUND((W17/($E52/$D52))*K52,0)</f>
-        <v>62</v>
+        <f>ROUND((W17/(($E52/$D52)*($C52/$B52)))*K52,0)</f>
+        <v>44</v>
       </c>
       <c r="T52">
-        <f>ROUND((X17/($E52/$D52))*L52,0)</f>
-        <v>12</v>
+        <f>ROUND((X17/(($E52/$D52)*($C52/$B52)))*L52,0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -7128,9 +7352,11 @@
         <f>ROUND((D53*B19)/(C53/B53),0)</f>
         <v>9</v>
       </c>
+      <c r="G53" s="8"/>
       <c r="M53">
         <v>33</v>
       </c>
+      <c r="O53" s="8"/>
       <c r="U53">
         <f>ROUND((Y19/(($E53/$D53)*($C53/$B53)))*M53,0)</f>
         <v>33</v>
@@ -7153,9 +7379,11 @@
         <f>ROUND(D54*B18,0)</f>
         <v>10</v>
       </c>
+      <c r="G54" s="8"/>
       <c r="H54">
         <v>100</v>
       </c>
+      <c r="O54" s="8"/>
       <c r="P54" s="8">
         <f>ROUND((T18/($E54/$D54))*H54,0)</f>
         <v>104</v>
@@ -7170,22 +7398,23 @@
       </c>
       <c r="C55">
         <f>dist_calculations!E8</f>
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D55">
         <v>10</v>
       </c>
       <c r="E55">
         <f>ROUND((D55*B20)/(C55/B55),0)</f>
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G55" s="8"/>
       <c r="I55">
         <v>100</v>
       </c>
-      <c r="P55" s="12"/>
+      <c r="O55" s="8"/>
       <c r="Q55">
         <f>ROUND((U20/(($E55/$D55)*($C55/$B55)))*I55,0)</f>
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -7230,15 +7459,12 @@
       <c r="B57">
         <v>27</v>
       </c>
-      <c r="C57">
-        <v>12</v>
-      </c>
       <c r="D57">
         <v>3</v>
       </c>
       <c r="E57">
-        <f>ROUND((D57*B22)/(C57/B57),0)</f>
-        <v>4</v>
+        <f>ROUND((D57*B22)/(C58/B57),0)</f>
+        <v>2</v>
       </c>
       <c r="G57" s="8"/>
       <c r="J57">
@@ -7246,8 +7472,8 @@
       </c>
       <c r="O57" s="8"/>
       <c r="R57">
-        <f>ROUND((V22/(($E57/$D57)*($C57/$B57)))*J57,0)</f>
-        <v>111</v>
+        <f>ROUND((V22/(($E57/$D57)*($C58/$B57)))*J57,0)</f>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -7257,17 +7483,24 @@
       <c r="B58">
         <v>27</v>
       </c>
+      <c r="C58">
+        <f>dist_calculations!E20</f>
+        <v>28</v>
+      </c>
       <c r="D58">
         <v>3</v>
       </c>
       <c r="E58">
-        <f>ROUND(D58*B23,0)</f>
-        <v>4</v>
+        <f t="shared" ref="E58:E67" si="4">ROUND((D58*B23)/(C58/B58),0)</f>
+        <v>3</v>
       </c>
       <c r="G58" s="8">
         <v>100</v>
       </c>
-      <c r="O58" s="8"/>
+      <c r="O58" s="8">
+        <f>ROUND((S23/(($E58/$D58)*($C58/$B58)))*G58,0)</f>
+        <v>101</v>
+      </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -7278,14 +7511,14 @@
       </c>
       <c r="C59">
         <f>dist_calculations!E17</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D59">
         <v>12</v>
       </c>
       <c r="E59">
-        <f>ROUND((D59*B24)/(C59/B59),0)</f>
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>22</v>
       </c>
       <c r="G59" s="8">
         <v>16</v>
@@ -7299,9 +7532,9 @@
       <c r="L59">
         <v>16</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="8">
         <f>ROUND((S24/(($E59/$D59)*($C59/$B59)))*G59,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q59">
         <f>ROUND((U24/(($E59/$D59)*($C59/$B59)))*I59,0)</f>
@@ -7309,7 +7542,7 @@
       </c>
       <c r="S59">
         <f>ROUND((W24/(($E59/$D59)*($C59/$B59)))*K59,0)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T59">
         <f>ROUND((X24/(($E59/$D59)*($C59/$B59)))*L59,0)</f>
@@ -7331,12 +7564,14 @@
         <v>8</v>
       </c>
       <c r="E60">
-        <f>ROUND((D60*B25)/(C60/B60),0)</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
+      <c r="G60" s="8"/>
       <c r="M60">
         <v>33</v>
       </c>
+      <c r="O60" s="8"/>
       <c r="U60">
         <f>ROUND((Y25/(($E60/$D60)*($C60/$B60)))*M60,0)</f>
         <v>33</v>
@@ -7351,21 +7586,23 @@
       </c>
       <c r="C61">
         <f>dist_calculations!E9</f>
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>15</v>
       </c>
       <c r="E61">
-        <f>ROUND((D61*B26)/(C61/B61),0)</f>
-        <v>9</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="G61" s="8"/>
       <c r="I61">
         <v>100</v>
       </c>
+      <c r="O61" s="8"/>
       <c r="Q61">
         <f>ROUND((U26/(($E61/$D61)*($C61/$B61)))*I61,0)</f>
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -7383,7 +7620,7 @@
         <v>6</v>
       </c>
       <c r="E62">
-        <f>ROUND((D62*B27)/(C62/B62),0)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="G62" s="8"/>
@@ -7417,7 +7654,7 @@
         <v>4</v>
       </c>
       <c r="E63">
-        <f>ROUND((D63*B28)/(C63/B63),0)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="G63" s="8"/>
@@ -7437,22 +7674,26 @@
       <c r="B64">
         <v>12</v>
       </c>
+      <c r="C64">
+        <f>dist_calculations!E21</f>
+        <v>20</v>
+      </c>
       <c r="D64">
         <v>4</v>
       </c>
       <c r="E64">
-        <f>ROUND(D64*B29,0)</f>
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>4</v>
       </c>
       <c r="G64" s="8">
         <v>100</v>
       </c>
       <c r="O64" s="8">
-        <f>ROUND((S29/($E64/$D64))*G64,0)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" ref="O64:T66" si="5">ROUND((S29/(($E64/$D64)*($C64/$B64)))*G64,0)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>31</v>
       </c>
@@ -7460,14 +7701,14 @@
         <v>9</v>
       </c>
       <c r="C65">
-        <f>dist_calculations!E22</f>
+        <f>dist_calculations!E25</f>
         <v>8</v>
       </c>
       <c r="D65">
         <v>7</v>
       </c>
       <c r="E65">
-        <f>ROUND((D65*B30)/(C65/B65),0)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="G65" s="8">
@@ -7491,28 +7732,28 @@
       <c r="M65">
         <v>20</v>
       </c>
-      <c r="O65">
-        <f>ROUND((S30/(($E65/$D65)*($C65/$B65)))*G65,0)</f>
-        <v>12</v>
+      <c r="O65" s="8">
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="P65">
-        <f>ROUND((T30/(($E65/$D65)*($C65/$B65)))*H65,0)</f>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="Q65">
-        <f>ROUND((U30/(($E65/$D65)*($C65/$B65)))*I65,0)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="R65">
-        <f>ROUND((V30/(($E65/$D65)*($C65/$B65)))*J65,0)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S65">
-        <f>ROUND((W30/(($E65/$D65)*($C65/$B65)))*K65,0)</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="T65">
-        <f>ROUND((X30/(($E65/$D65)*($C65/$B65)))*L65,0)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="U65">
@@ -7520,7 +7761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>29</v>
       </c>
@@ -7528,14 +7769,14 @@
         <v>14</v>
       </c>
       <c r="C66">
-        <f>dist_calculations!E24</f>
+        <f>dist_calculations!E27</f>
         <v>38</v>
       </c>
       <c r="D66">
         <v>14</v>
       </c>
       <c r="E66">
-        <f>ROUND((D66*B31)/(C66/B66),0)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="G66" s="8">
@@ -7559,28 +7800,28 @@
       <c r="M66">
         <v>20</v>
       </c>
-      <c r="O66">
-        <f>ROUND((S31/(($E66/$D66)*($C66/$B66)))*G66,0)</f>
-        <v>16</v>
+      <c r="O66" s="8">
+        <f t="shared" si="5"/>
+        <v>15</v>
       </c>
       <c r="P66">
-        <f>ROUND((T31/(($E66/$D66)*($C66/$B66)))*H66,0)</f>
+        <f t="shared" si="5"/>
         <v>35</v>
       </c>
       <c r="Q66">
-        <f>ROUND((U31/(($E66/$D66)*($C66/$B66)))*I66,0)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="R66">
-        <f>ROUND((V31/(($E66/$D66)*($C66/$B66)))*J66,0)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="S66">
-        <f>ROUND((W31/(($E66/$D66)*($C66/$B66)))*K66,0)</f>
+        <f t="shared" si="5"/>
         <v>32</v>
       </c>
       <c r="T66">
-        <f>ROUND((X31/(($E66/$D66)*($C66/$B66)))*L66,0)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="U66">
@@ -7588,7 +7829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>156</v>
       </c>
@@ -7596,40 +7837,41 @@
         <v>2</v>
       </c>
       <c r="C67">
-        <f>dist_calculations!E26</f>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D67">
         <v>8</v>
       </c>
       <c r="E67">
-        <f>ROUND((D67*B32)/(C67/B67),0)</f>
-        <v>1</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G67" s="8"/>
       <c r="H67">
         <v>18</v>
       </c>
       <c r="M67">
         <v>26</v>
       </c>
+      <c r="O67" s="8"/>
       <c r="P67">
         <f>ROUND((T32/(($E67/$D67)*($C67/$B67)))*H67,0)</f>
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="U67">
         <f>ROUND((Y32/(($E67/$D67)*($C67/$B67)))*M67,0)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>151</v>
       </c>
       <c r="B68">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="C68">
-        <f>dist_calculations!E28</f>
+        <f>dist_calculations!E31</f>
         <v>15</v>
       </c>
       <c r="D68">
@@ -7661,43 +7903,44 @@
         <v>20</v>
       </c>
       <c r="O68" s="8">
-        <f>ROUND((S33/($E68/$D68))*G68,0)</f>
+        <f t="shared" ref="O68:U69" si="6">ROUND((S33/($E68/$D68))*G68,0)</f>
         <v>16</v>
       </c>
-      <c r="P68" s="8">
-        <f>ROUND((T33/($E68/$D68))*H68,0)</f>
+      <c r="P68" s="11">
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
-      <c r="Q68" s="8">
-        <f>ROUND((U33/($E68/$D68))*I68,0)</f>
+      <c r="Q68" s="11">
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="R68" s="8">
-        <f>ROUND((V33/($E68/$D68))*J68,0)</f>
+      <c r="R68" s="11">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="S68" s="8">
-        <f>ROUND((W33/($E68/$D68))*K68,0)</f>
+      <c r="S68" s="11">
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="T68" s="8">
-        <f>ROUND((X33/($E68/$D68))*L68,0)</f>
+      <c r="T68" s="11">
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="U68" s="8">
-        <f>ROUND((Y33/($E68/$D68))*M68,0)</f>
+      <c r="U68" s="11">
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V68" s="11"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>30</v>
       </c>
       <c r="B69">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C69">
-        <f>dist_calculations!E29</f>
+        <f>dist_calculations!E32</f>
         <v>10</v>
       </c>
       <c r="D69">
@@ -7729,40 +7972,41 @@
         <v>20</v>
       </c>
       <c r="O69" s="8">
-        <f>ROUND((S34/($E69/$D69))*G69,0)</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="P69" s="8">
-        <f>ROUND((T34/($E69/$D69))*H69,0)</f>
+      <c r="P69" s="11">
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="Q69" s="8">
-        <f>ROUND((U34/($E69/$D69))*I69,0)</f>
+      <c r="Q69" s="11">
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="R69" s="8">
-        <f>ROUND((V34/($E69/$D69))*J69,0)</f>
+      <c r="R69" s="11">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="S69" s="8">
-        <f>ROUND((W34/($E69/$D69))*K69,0)</f>
+      <c r="S69" s="11">
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
-      <c r="T69" s="8">
-        <f>ROUND((X34/($E69/$D69))*L69,0)</f>
+      <c r="T69" s="11">
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="U69" s="8">
-        <f>ROUND((Y34/($E69/$D69))*M69,0)</f>
+      <c r="U69" s="11">
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V69" s="11"/>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>12</v>
       </c>
@@ -7791,299 +8035,299 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
       <c r="B73">
         <f>$E38*2*O38/100</f>
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="C73">
-        <f t="shared" ref="C73:I73" si="0">$E38*2*P38/100</f>
+        <f t="shared" ref="C73:I73" si="7">$E38*2*P38/100</f>
         <v>0</v>
       </c>
       <c r="D73">
-        <f t="shared" si="0"/>
-        <v>5.2</v>
+        <f t="shared" si="7"/>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F73">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>1.52</v>
       </c>
       <c r="G73">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <f t="shared" si="7"/>
+        <v>1.28</v>
       </c>
       <c r="H73">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I73">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>78</v>
       </c>
       <c r="B74">
-        <f t="shared" ref="B74:I74" si="1">$E39*2*O39/100</f>
+        <f t="shared" ref="B74:I74" si="8">$E39*2*O39/100</f>
         <v>0</v>
       </c>
       <c r="C74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>12.24</v>
       </c>
       <c r="D74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I74">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>152</v>
       </c>
       <c r="B75">
-        <f t="shared" ref="B75:I75" si="2">$E40*2*O40/100</f>
+        <f t="shared" ref="B75:I75" si="9">$E40*2*O40/100</f>
         <v>0</v>
       </c>
       <c r="C75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>3.3</v>
       </c>
       <c r="I75">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>49</v>
       </c>
       <c r="B76">
-        <f t="shared" ref="B76:I76" si="3">$E41*2*O41/100</f>
+        <f t="shared" ref="B76:I76" si="10">$E41*2*O41/100</f>
         <v>0</v>
       </c>
       <c r="C76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="D76">
-        <f t="shared" si="3"/>
-        <v>8.9600000000000009</v>
+        <f t="shared" si="10"/>
+        <v>12.84</v>
       </c>
       <c r="E76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I76">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>59</v>
       </c>
       <c r="B77">
-        <f t="shared" ref="B77:I77" si="4">$E42*2*O42/100</f>
+        <f t="shared" ref="B77:I77" si="11">$E42*2*O42/100</f>
         <v>0</v>
       </c>
       <c r="C77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="D77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F77">
-        <f t="shared" si="4"/>
-        <v>5.94</v>
+        <f t="shared" si="11"/>
+        <v>8.8800000000000008</v>
       </c>
       <c r="G77">
-        <f t="shared" si="4"/>
-        <v>5.16</v>
+        <f t="shared" si="11"/>
+        <v>5.12</v>
       </c>
       <c r="H77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I77">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>55</v>
       </c>
       <c r="B78">
-        <f t="shared" ref="B78:I78" si="5">$E43*2*O43/100</f>
+        <f t="shared" ref="B78:I78" si="12">$E43*2*O43/100</f>
         <v>0</v>
       </c>
       <c r="C78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>7.12</v>
       </c>
       <c r="F78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I78">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>21</v>
       </c>
       <c r="B79">
-        <f t="shared" ref="B79:I79" si="6">$E44*2*O44/100</f>
-        <v>1.26</v>
+        <f t="shared" ref="B79:I79" si="13">$E44*2*O44/100</f>
+        <v>3.44</v>
       </c>
       <c r="C79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="D79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H79">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I79">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>22</v>
       </c>
       <c r="B80">
-        <f t="shared" ref="B80:I80" si="7">$E45*2*O45/100</f>
-        <v>2.4</v>
+        <f t="shared" ref="B80:I80" si="14">$E45*2*O45/100</f>
+        <v>2.52</v>
       </c>
       <c r="C80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="D80">
-        <f t="shared" si="7"/>
-        <v>1.6</v>
+        <f t="shared" si="14"/>
+        <v>1.26</v>
       </c>
       <c r="E80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="F80">
-        <f t="shared" si="7"/>
-        <v>5.6</v>
+        <f t="shared" si="14"/>
+        <v>6.3</v>
       </c>
       <c r="G80">
-        <f t="shared" si="7"/>
-        <v>1.92</v>
+        <f t="shared" si="14"/>
+        <v>2.16</v>
       </c>
       <c r="H80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
@@ -8092,35 +8336,35 @@
         <v>153</v>
       </c>
       <c r="B81">
-        <f t="shared" ref="B81:I81" si="8">$E46*2*O46/100</f>
+        <f t="shared" ref="B81:I81" si="15">$E46*2*O46/100</f>
         <v>0</v>
       </c>
       <c r="C81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="D81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>4.62</v>
       </c>
       <c r="I81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -8129,35 +8373,35 @@
         <v>79</v>
       </c>
       <c r="B82">
-        <f t="shared" ref="B82:I82" si="9">$E47*2*O47/100</f>
+        <f t="shared" ref="B82:I82" si="16">$E47*2*O47/100</f>
         <v>0</v>
       </c>
       <c r="C82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>14.84</v>
       </c>
       <c r="D82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="I82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
@@ -8166,35 +8410,35 @@
         <v>50</v>
       </c>
       <c r="B83">
-        <f t="shared" ref="B83:I83" si="10">$E48*2*O48/100</f>
+        <f t="shared" ref="B83:I83" si="17">$E48*2*O48/100</f>
         <v>0</v>
       </c>
       <c r="C83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="D83">
-        <f t="shared" si="10"/>
-        <v>10.1</v>
+        <f t="shared" si="17"/>
+        <v>7.52</v>
       </c>
       <c r="E83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -8203,35 +8447,35 @@
         <v>116</v>
       </c>
       <c r="B84">
-        <f t="shared" ref="B84:I84" si="11">$E49*2*O49/100</f>
+        <f t="shared" ref="B84:I84" si="18">$E49*2*O49/100</f>
         <v>0</v>
       </c>
       <c r="C84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="E84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>7.68</v>
       </c>
       <c r="G84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>6.56</v>
       </c>
       <c r="H84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -8240,35 +8484,35 @@
         <v>56</v>
       </c>
       <c r="B85">
-        <f t="shared" ref="B85:I85" si="12">$E50*2*O50/100</f>
+        <f t="shared" ref="B85:I85" si="19">$E50*2*O50/100</f>
         <v>0</v>
       </c>
       <c r="C85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>8.24</v>
       </c>
       <c r="F85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="G85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -8277,35 +8521,35 @@
         <v>23</v>
       </c>
       <c r="B86">
-        <f t="shared" ref="B86:I86" si="13">$E51*2*O51/100</f>
-        <v>3.72</v>
+        <f t="shared" ref="B86:I86" si="20">$E51*2*O51/100</f>
+        <v>4.4400000000000004</v>
       </c>
       <c r="C86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="G86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="I86">
-        <f t="shared" si="13"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -8314,35 +8558,35 @@
         <v>26</v>
       </c>
       <c r="B87">
-        <f t="shared" ref="B87:I87" si="14">$E52*2*O52/100</f>
-        <v>3.4</v>
+        <f t="shared" ref="B87:I87" si="21">$E52*2*O52/100</f>
+        <v>2.8</v>
       </c>
       <c r="C87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D87">
-        <f t="shared" si="14"/>
-        <v>1.4</v>
+        <f t="shared" si="21"/>
+        <v>1.1200000000000001</v>
       </c>
       <c r="E87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F87">
-        <f t="shared" si="14"/>
-        <v>12.4</v>
+        <f t="shared" si="21"/>
+        <v>12.32</v>
       </c>
       <c r="G87">
-        <f t="shared" si="14"/>
-        <v>2.4</v>
+        <f t="shared" si="21"/>
+        <v>2.52</v>
       </c>
       <c r="H87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I87">
-        <f t="shared" si="14"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -8351,35 +8595,35 @@
         <v>154</v>
       </c>
       <c r="B88">
-        <f t="shared" ref="B88:I88" si="15">$E53*2*O53/100</f>
+        <f t="shared" ref="B88:I88" si="22">$E53*2*O53/100</f>
         <v>0</v>
       </c>
       <c r="C88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="D88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="G88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>5.94</v>
       </c>
       <c r="I88">
-        <f t="shared" si="15"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -8388,35 +8632,35 @@
         <v>80</v>
       </c>
       <c r="B89">
-        <f t="shared" ref="B89:I89" si="16">$E54*2*O54/100</f>
+        <f t="shared" ref="B89:I89" si="23">$E54*2*O54/100</f>
         <v>0</v>
       </c>
       <c r="C89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>20.8</v>
       </c>
       <c r="D89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="E89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="G89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I89">
-        <f t="shared" si="16"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -8425,35 +8669,35 @@
         <v>51</v>
       </c>
       <c r="B90">
-        <f t="shared" ref="B90:I90" si="17">$E55*2*O55/100</f>
+        <f t="shared" ref="B90:I90" si="24">$E55*2*O55/100</f>
         <v>0</v>
       </c>
       <c r="C90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D90">
-        <f t="shared" si="17"/>
-        <v>14.7</v>
+        <f t="shared" si="24"/>
+        <v>10.1</v>
       </c>
       <c r="E90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I90">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
     </row>
@@ -8462,35 +8706,35 @@
         <v>61</v>
       </c>
       <c r="B91">
-        <f t="shared" ref="B91:I91" si="18">$E56*2*O56/100</f>
+        <f t="shared" ref="B91:I91" si="25">$E56*2*O56/100</f>
         <v>0</v>
       </c>
       <c r="C91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="D91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>16.8</v>
       </c>
       <c r="G91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>9.76</v>
       </c>
       <c r="H91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="I91">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
@@ -8499,35 +8743,35 @@
         <v>57</v>
       </c>
       <c r="B92">
-        <f t="shared" ref="B92:I92" si="19">$E57*2*O57/100</f>
+        <f t="shared" ref="B92:I92" si="26">$E57*2*O57/100</f>
         <v>0</v>
       </c>
       <c r="C92">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="D92">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E92">
-        <f t="shared" si="19"/>
-        <v>8.8800000000000008</v>
+        <f t="shared" si="26"/>
+        <v>3.8</v>
       </c>
       <c r="F92">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G92">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H92">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I92">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -8536,35 +8780,35 @@
         <v>24</v>
       </c>
       <c r="B93">
-        <f t="shared" ref="B93:I93" si="20">$E58*2*O58/100</f>
-        <v>0</v>
+        <f t="shared" ref="B93:I93" si="27">$E58*2*O58/100</f>
+        <v>6.06</v>
       </c>
       <c r="C93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="D93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="E93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="F93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="G93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I93">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -8573,35 +8817,35 @@
         <v>27</v>
       </c>
       <c r="B94">
-        <f t="shared" ref="B94:I94" si="21">$E59*2*O59/100</f>
-        <v>4.5</v>
+        <f t="shared" ref="B94:I94" si="28">$E59*2*O59/100</f>
+        <v>6.16</v>
       </c>
       <c r="C94">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D94">
-        <f t="shared" si="21"/>
-        <v>0.9</v>
+        <f t="shared" si="28"/>
+        <v>1.32</v>
       </c>
       <c r="E94">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="F94">
-        <f t="shared" si="21"/>
-        <v>12.6</v>
+        <f t="shared" si="28"/>
+        <v>18.920000000000002</v>
       </c>
       <c r="G94">
-        <f t="shared" si="21"/>
-        <v>2.4</v>
+        <f t="shared" si="28"/>
+        <v>3.52</v>
       </c>
       <c r="H94">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="I94">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
     </row>
@@ -8610,35 +8854,35 @@
         <v>155</v>
       </c>
       <c r="B95">
-        <f t="shared" ref="B95:I95" si="22">$E60*2*O60/100</f>
+        <f t="shared" ref="B95:I95" si="29">$E60*2*O60/100</f>
         <v>0</v>
       </c>
       <c r="C95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="G95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>6.6</v>
       </c>
       <c r="I95">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
@@ -8647,35 +8891,35 @@
         <v>52</v>
       </c>
       <c r="B96">
-        <f t="shared" ref="B96:I96" si="23">$E61*2*O61/100</f>
+        <f t="shared" ref="B96:I96" si="30">$E61*2*O61/100</f>
         <v>0</v>
       </c>
       <c r="C96">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="D96">
-        <f t="shared" si="23"/>
-        <v>17.28</v>
+        <f t="shared" si="30"/>
+        <v>12.36</v>
       </c>
       <c r="E96">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F96">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G96">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H96">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I96">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -8684,35 +8928,35 @@
         <v>62</v>
       </c>
       <c r="B97">
-        <f t="shared" ref="B97:I97" si="24">$E62*2*O62/100</f>
+        <f t="shared" ref="B97:I97" si="31">$E62*2*O62/100</f>
         <v>0</v>
       </c>
       <c r="C97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="D97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="E97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="F97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>15.36</v>
       </c>
       <c r="G97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>12.32</v>
       </c>
       <c r="H97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="I97">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -8721,35 +8965,35 @@
         <v>58</v>
       </c>
       <c r="B98">
-        <f t="shared" ref="B98:I98" si="25">$E63*2*O63/100</f>
+        <f t="shared" ref="B98:I98" si="32">$E63*2*O63/100</f>
         <v>0</v>
       </c>
       <c r="C98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="D98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="E98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>12</v>
       </c>
       <c r="F98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="G98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I98">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -8758,35 +9002,35 @@
         <v>25</v>
       </c>
       <c r="B99">
-        <f t="shared" ref="B99:I99" si="26">$E64*2*O64/100</f>
-        <v>14</v>
+        <f t="shared" ref="B99:I99" si="33">$E64*2*O64/100</f>
+        <v>7.92</v>
       </c>
       <c r="C99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="D99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="E99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="F99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="G99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="H99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="I99">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
     </row>
@@ -8795,35 +9039,35 @@
         <v>31</v>
       </c>
       <c r="B100">
-        <f t="shared" ref="B100:I100" si="27">$E65*2*O65/100</f>
-        <v>1.92</v>
+        <f t="shared" ref="B100:I100" si="34">$E65*2*O65/100</f>
+        <v>1.76</v>
       </c>
       <c r="C100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>5.76</v>
       </c>
       <c r="D100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0.8</v>
       </c>
       <c r="E100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0.48</v>
       </c>
       <c r="F100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>4.32</v>
       </c>
       <c r="G100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>1.28</v>
       </c>
       <c r="H100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>2.88</v>
       </c>
       <c r="I100">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -8832,35 +9076,35 @@
         <v>29</v>
       </c>
       <c r="B101">
-        <f t="shared" ref="B101:I101" si="28">$E66*2*O66/100</f>
-        <v>1.92</v>
+        <f t="shared" ref="B101:I101" si="35">$E66*2*O66/100</f>
+        <v>1.8</v>
       </c>
       <c r="C101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>4.2</v>
       </c>
       <c r="D101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0.48</v>
       </c>
       <c r="E101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0.84</v>
       </c>
       <c r="F101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>3.84</v>
       </c>
       <c r="G101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>1.56</v>
       </c>
       <c r="H101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>1.2</v>
       </c>
       <c r="I101">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
     </row>
@@ -8869,35 +9113,35 @@
         <v>156</v>
       </c>
       <c r="B102">
-        <f t="shared" ref="B102:I102" si="29">$E67*2*O67/100</f>
+        <f t="shared" ref="B102:I102" si="36">$E67*2*O67/100</f>
         <v>0</v>
       </c>
       <c r="C102">
-        <f t="shared" si="29"/>
-        <v>0.56000000000000005</v>
+        <f t="shared" si="36"/>
+        <v>3.04</v>
       </c>
       <c r="D102">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="F102">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="G102">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H102">
-        <f t="shared" si="29"/>
-        <v>0.66</v>
+        <f t="shared" si="36"/>
+        <v>3.52</v>
       </c>
       <c r="I102">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -8906,35 +9150,35 @@
         <v>151</v>
       </c>
       <c r="B103">
-        <f t="shared" ref="B103:I103" si="30">$E68*2*O68/100</f>
+        <f t="shared" ref="B103:I103" si="37">$E68*2*O68/100</f>
         <v>4.4800000000000004</v>
       </c>
       <c r="C103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>7.84</v>
       </c>
       <c r="D103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>1.4</v>
       </c>
       <c r="E103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="F103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>8.68</v>
       </c>
       <c r="G103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>4.4800000000000004</v>
       </c>
       <c r="H103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>5.6</v>
       </c>
       <c r="I103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
@@ -8943,35 +9187,35 @@
         <v>30</v>
       </c>
       <c r="B104">
-        <f t="shared" ref="B104:I104" si="31">$E69*2*O69/100</f>
+        <f t="shared" ref="B104:I104" si="38">$E69*2*O69/100</f>
         <v>13.44</v>
       </c>
       <c r="C104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>24.36</v>
       </c>
       <c r="D104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>4.2</v>
       </c>
       <c r="E104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>6.72</v>
       </c>
       <c r="F104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>26.04</v>
       </c>
       <c r="G104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>13.44</v>
       </c>
       <c r="H104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>15.96</v>
       </c>
       <c r="I104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
     </row>
@@ -8982,7 +9226,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92AB93CD-F488-4A49-9F28-018FA4EFE61D}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -9054,7 +9298,8 @@
         <v>48</v>
       </c>
       <c r="I2">
-        <v>72</v>
+        <f>(G20/C20)*H2</f>
+        <v>55.29161825631887</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9085,7 +9330,8 @@
         <v>24</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <f>((G20)/(C20))*H3</f>
+        <v>27.645809128159435</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -9116,7 +9362,8 @@
         <v>57.6</v>
       </c>
       <c r="I4">
-        <v>54</v>
+        <f>(G22/C22)*H4</f>
+        <v>50.928693373621392</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -9147,7 +9394,8 @@
         <v>60</v>
       </c>
       <c r="I5">
-        <v>56</v>
+        <f>(G22/C22)*H5</f>
+        <v>53.050722264188948</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -9178,8 +9426,8 @@
         <v>12.8</v>
       </c>
       <c r="I6">
-        <f>(G$25/C$25)*H6</f>
-        <v>16.873956940808974</v>
+        <f>(G$26/C$26)*H6</f>
+        <v>13.381047854061519</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -9210,8 +9458,8 @@
         <v>81</v>
       </c>
       <c r="I7">
-        <f>(G$25/C$25)*H7</f>
-        <v>106.78050876605678</v>
+        <f>(G$26/C$26)*H7</f>
+        <v>84.676943451483041</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -9242,8 +9490,8 @@
         <v>7.68</v>
       </c>
       <c r="I8">
-        <f>(G$29/C$29)*H8</f>
-        <v>13.498277739832433</v>
+        <f>(G$30/C$30)*H8</f>
+        <v>12.624045463478957</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -9274,8 +9522,8 @@
         <v>48</v>
       </c>
       <c r="I9">
-        <f>(G$29/C$29)*H9</f>
-        <v>84.364235873952708</v>
+        <f>(G$30/C$30)*H9</f>
+        <v>78.900284146743473</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9306,8 +9554,8 @@
         <v>10.08</v>
       </c>
       <c r="I10">
-        <f>(G$31/C$31)*H10</f>
-        <v>7.4279381204819153</v>
+        <f>((G$31)/C$31)*H10</f>
+        <v>7.3453667003720486</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -9325,7 +9573,7 @@
         <v>1975</v>
       </c>
       <c r="E11">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F11">
@@ -9339,8 +9587,8 @@
         <v>85.12</v>
       </c>
       <c r="I11">
-        <f>(G$32/C$32)*H11</f>
-        <v>97.863608655259725</v>
+        <f>((G$33-I10)/C$33)*H11</f>
+        <v>91.295986664338812</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -9358,7 +9606,7 @@
         <v>2000</v>
       </c>
       <c r="E12">
-        <f>dist_calculations!E$28</f>
+        <f>dist_calculations!E$31</f>
         <v>15</v>
       </c>
       <c r="F12">
@@ -9373,7 +9621,7 @@
         <v>33.6</v>
       </c>
       <c r="I12">
-        <f>(G$36/C$36)*H12</f>
+        <f>(G$37/C$37)*H12</f>
         <v>33.6</v>
       </c>
     </row>
@@ -9392,7 +9640,7 @@
         <v>1997.5</v>
       </c>
       <c r="E13">
-        <f>dist_calculations!E$29</f>
+        <f>dist_calculations!E$32</f>
         <v>10</v>
       </c>
       <c r="F13">
@@ -9406,7 +9654,7 @@
         <v>67.2</v>
       </c>
       <c r="I13">
-        <f>(G$35/C$35)*H13</f>
+        <f>(G$36/C$36)*H13</f>
         <v>67.661478411015523</v>
       </c>
     </row>
@@ -9449,7 +9697,7 @@
       </c>
       <c r="H17">
         <f>I2</f>
-        <v>72</v>
+        <v>55.29161825631887</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -9465,16 +9713,16 @@
         <v>28000</v>
       </c>
       <c r="F18">
-        <f>(D18/D$36)*F$36</f>
+        <f>(D18/D$37)*F$37</f>
         <v>68.362534936101454</v>
       </c>
       <c r="G18">
-        <f>(F18/F$36)*C$36</f>
+        <f t="shared" ref="G18:G37" si="2">(F18/F$37)*C$37</f>
         <v>68.909435215590264</v>
       </c>
       <c r="H18">
         <f>I2</f>
-        <v>72</v>
+        <v>55.29161825631887</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -9486,20 +9734,20 @@
         <v>72</v>
       </c>
       <c r="E19">
-        <f>_xlfn.FORECAST.LINEAR(B19,D$17:D$22,B$17:B$22)</f>
+        <f>_xlfn.FORECAST.LINEAR(B19,D$17:D$23,B$17:B$23)</f>
         <v>31800</v>
       </c>
       <c r="F19">
-        <f>(E19/D$36)*F$36</f>
+        <f>(E19/D$37)*F$37</f>
         <v>77.640307534572372</v>
       </c>
       <c r="G19">
-        <f>(F19/F$36)*C$36</f>
+        <f t="shared" si="2"/>
         <v>78.261429994848967</v>
       </c>
       <c r="H19">
         <f>I2+I3</f>
-        <v>87</v>
+        <v>82.937427384478298</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -9511,20 +9759,20 @@
         <v>72</v>
       </c>
       <c r="E20">
-        <f>_xlfn.FORECAST.LINEAR(B20,D$17:D$22,B$17:B$22)</f>
+        <f>_xlfn.FORECAST.LINEAR(B20,D$17:D$23,B$17:B$23)</f>
         <v>33700</v>
       </c>
       <c r="F20">
-        <f>(E20/D$36)*F$36</f>
+        <f>(E20/D$37)*F$37</f>
         <v>82.279193833807824</v>
       </c>
       <c r="G20">
-        <f>(F20/F$36)*C$36</f>
+        <f t="shared" si="2"/>
         <v>82.937427384478298</v>
       </c>
       <c r="H20">
         <f>I2+I3</f>
-        <v>87</v>
+        <v>82.937427384478298</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -9536,409 +9784,434 @@
         <v>117.6</v>
       </c>
       <c r="E21">
-        <f>_xlfn.FORECAST.LINEAR(B21,D$17:D$22,B$17:B$22)</f>
+        <f>_xlfn.FORECAST.LINEAR(B21,D$17:D$23,B$17:B$23)</f>
         <v>35600</v>
       </c>
       <c r="F21">
-        <f>(E21/D$36)*F$36</f>
+        <f>(E21/D$37)*F$37</f>
         <v>86.91808013304329</v>
       </c>
       <c r="G21">
-        <f>(F21/F$36)*C$36</f>
+        <f t="shared" si="2"/>
         <v>87.613424774107642</v>
       </c>
       <c r="H21">
         <f>I4+I5</f>
-        <v>110</v>
+        <v>103.97941563781035</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="C22">
         <f>H4+H5</f>
         <v>117.6</v>
       </c>
-      <c r="D22">
-        <f>sources_consumption!D9</f>
-        <v>43200</v>
+      <c r="E22">
+        <f>_xlfn.FORECAST.LINEAR(B22,D$17:D$23,B$17:B$23)</f>
+        <v>42250</v>
       </c>
       <c r="F22">
-        <f>(D22/D$36)*F$36</f>
-        <v>105.47362532998513</v>
+        <f>(E22/D$37)*F$37</f>
+        <v>103.15418218036739</v>
       </c>
       <c r="G22">
-        <f>(F22/F$36)*C$36</f>
-        <v>106.31741433262502</v>
+        <f t="shared" si="2"/>
+        <v>103.97941563781033</v>
       </c>
       <c r="H22">
         <f>I4+I5</f>
-        <v>110</v>
+        <v>103.97941563781035</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B23">
-        <v>1900</v>
+        <v>1880</v>
       </c>
       <c r="C23">
         <f>H4+H5</f>
         <v>117.6</v>
       </c>
-      <c r="E23">
-        <f>_xlfn.FORECAST.LINEAR(B23,D$22:D$24,B$22:B$24)</f>
-        <v>45866.666666666657</v>
+      <c r="D23">
+        <f>sources_consumption!D9</f>
+        <v>43200</v>
       </c>
       <c r="F23">
-        <f>(E23/D$36)*F$36</f>
-        <v>111.98434294294712</v>
+        <f>(D23/D$37)*F$37</f>
+        <v>105.47362532998513</v>
       </c>
       <c r="G23">
-        <f>(F23/F$36)*C$36</f>
-        <v>112.88021768649071</v>
+        <f t="shared" si="2"/>
+        <v>106.31741433262502</v>
       </c>
       <c r="H23">
         <f>I4+I5</f>
-        <v>110</v>
+        <v>103.97941563781035</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B24">
+        <v>1900</v>
+      </c>
+      <c r="C24">
+        <f>H4+H5</f>
+        <v>117.6</v>
+      </c>
+      <c r="E24">
+        <f>_xlfn.FORECAST.LINEAR(B24,D$23:D$25,B$23:B$25)</f>
+        <v>39353.066666666651</v>
+      </c>
+      <c r="F24">
+        <f>(E24/D$37)*F$37</f>
+        <v>96.081264101526031</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="2"/>
+        <v>96.849914214338256</v>
+      </c>
+      <c r="H24">
+        <f>I4+I5</f>
+        <v>103.97941563781035</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25">
         <v>1910</v>
-      </c>
-      <c r="C24">
-        <f>H6+H7</f>
-        <v>93.8</v>
-      </c>
-      <c r="D24">
-        <f>sources_consumption!D12</f>
-        <v>47200</v>
-      </c>
-      <c r="F24">
-        <f>(D24/D$36)*F$36</f>
-        <v>115.23970174942816</v>
-      </c>
-      <c r="G24">
-        <f>(F24/F$36)*C$36</f>
-        <v>116.16161936342361</v>
-      </c>
-      <c r="H24">
-        <f>I6+I7</f>
-        <v>123.65446570686575</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="1">
-        <v>1928</v>
       </c>
       <c r="C25">
         <f>H6+H7</f>
         <v>93.8</v>
       </c>
-      <c r="E25">
-        <f>_xlfn.FORECAST.LINEAR(B25,D$24:D$26,B$24:B$26)</f>
-        <v>50244.57142857142</v>
+      <c r="D25">
+        <f>sources_consumption!D12</f>
+        <v>37429.599999999999</v>
       </c>
       <c r="F25">
-        <f>(E25/D$36)*F$36</f>
-        <v>122.67308105839854</v>
+        <f>(D25/D$37)*F$37</f>
+        <v>91.385083487296555</v>
       </c>
       <c r="G25">
-        <f>(F25/F$36)*C$36</f>
-        <v>123.65446570686574</v>
+        <f t="shared" si="2"/>
+        <v>92.116164155194937</v>
       </c>
       <c r="H25">
         <f>I6+I7</f>
-        <v>123.65446570686575</v>
+        <v>98.057991305544562</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B26">
-        <v>1935</v>
+      <c r="B26" s="1">
+        <v>1928</v>
       </c>
       <c r="C26">
         <f>H6+H7</f>
         <v>93.8</v>
       </c>
-      <c r="D26">
-        <f>sources_consumption!D18</f>
-        <v>51428.571428571435</v>
+      <c r="E26">
+        <f>_xlfn.FORECAST.LINEAR(B26,D$25:D$27,B$25:B$27)</f>
+        <v>39843.945142857148</v>
       </c>
       <c r="F26">
-        <f>(D26/D$36)*F$36</f>
-        <v>125.56383967855371</v>
+        <f>(E26/D$37)*F$37</f>
+        <v>97.279753279310071</v>
       </c>
       <c r="G26">
-        <f>(F26/F$36)*C$36</f>
-        <v>126.56835039598215</v>
+        <f t="shared" si="2"/>
+        <v>98.057991305544562</v>
       </c>
       <c r="H26">
         <f>I6+I7</f>
-        <v>123.65446570686575</v>
+        <v>98.057991305544562</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B27">
-        <v>1945</v>
+        <v>1935</v>
       </c>
       <c r="C27">
-        <f>H8+H9</f>
-        <v>55.68</v>
-      </c>
-      <c r="E27">
-        <f>_xlfn.FORECAST.LINEAR(B27,D$26:D$31,B$26:B$31)</f>
-        <v>49642.448979591834</v>
+        <f>H6+H7</f>
+        <v>93.8</v>
+      </c>
+      <c r="D27">
+        <f>sources_consumption!D18</f>
+        <v>40782.857142857152</v>
       </c>
       <c r="F27">
-        <f>(E27/D$36)*F$36</f>
-        <v>121.20298759574932</v>
+        <f>(D27/D$37)*F$37</f>
+        <v>99.572124865093116</v>
       </c>
       <c r="G27">
-        <f>(F27/F$36)*C$36</f>
-        <v>122.17261149651533</v>
+        <f t="shared" si="2"/>
+        <v>100.36870186401387</v>
       </c>
       <c r="H27">
-        <f>I8+I9</f>
-        <v>97.86251361378514</v>
+        <f>I6+I7</f>
+        <v>98.057991305544562</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B28">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="C28">
         <f>H8+H9</f>
         <v>55.68</v>
       </c>
       <c r="E28">
-        <f>_xlfn.FORECAST.LINEAR(B28,D$26:D$31,B$26:B$31)</f>
-        <v>48749.387755102071</v>
+        <f>_xlfn.FORECAST.LINEAR(B28,D$27:D$32,B$27:B$32)</f>
+        <v>42038.367346938816</v>
       </c>
       <c r="F28">
-        <f>(E28/D$36)*F$36</f>
-        <v>119.02256155434723</v>
+        <f>(E28/D$37)*F$37</f>
+        <v>102.63747701470614</v>
       </c>
       <c r="G28">
-        <f>(F28/F$36)*C$36</f>
-        <v>119.97474204678203</v>
+        <f t="shared" si="2"/>
+        <v>103.4585768308238</v>
       </c>
       <c r="H28">
         <f>I8+I9</f>
-        <v>97.86251361378514</v>
+        <v>91.524329610222424</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>239</v>
-      </c>
-      <c r="B29" s="1">
+      <c r="B29">
+        <v>1950</v>
+      </c>
+      <c r="C29">
+        <f>H8+H9</f>
+        <v>55.68</v>
+      </c>
+      <c r="E29">
+        <f>_xlfn.FORECAST.LINEAR(B29,D$27:D$32,B$27:B$32)</f>
+        <v>42666.122448979644</v>
+      </c>
+      <c r="F29">
+        <f>(E29/D$37)*F$37</f>
+        <v>104.17015308951262</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="2"/>
+        <v>105.00351431422874</v>
+      </c>
+      <c r="H29">
+        <f>I8+I9</f>
+        <v>91.524329610222424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30" s="1">
         <v>1960</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <f>H8+H9+H10</f>
         <v>65.760000000000005</v>
       </c>
-      <c r="E29">
-        <f>_xlfn.FORECAST.LINEAR(B29,D$26:D$31,B$26:B$31)</f>
-        <v>46963.265306122485</v>
-      </c>
-      <c r="F29">
-        <f>(E29/D$36)*F$36</f>
-        <v>114.66170947154286</v>
-      </c>
-      <c r="G29">
-        <f>(F29/F$36)*C$36</f>
-        <v>115.57900314731522</v>
-      </c>
-      <c r="H29">
+      <c r="E30">
+        <f>_xlfn.FORECAST.LINEAR(B30,D$27:D$32,B$27:B$32)</f>
+        <v>43921.632653061271</v>
+      </c>
+      <c r="F30">
+        <f>(E30/D$37)*F$37</f>
+        <v>107.23550523912557</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="2"/>
+        <v>108.09338928103858</v>
+      </c>
+      <c r="H30">
         <f>I8+I9+I10</f>
-        <v>105.29045173426705</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+        <v>98.869696310594477</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B31" s="1">
         <v>1966</v>
-      </c>
-      <c r="C30">
-        <f>H8+H9+H10+H11</f>
-        <v>150.88</v>
-      </c>
-      <c r="E30">
-        <f>_xlfn.FORECAST.LINEAR(B30,D$26:D$31,B$26:B$31)</f>
-        <v>45891.591836734733</v>
-      </c>
-      <c r="F30">
-        <f>(E30/D$36)*F$36</f>
-        <v>112.04519822186026</v>
-      </c>
-      <c r="G30">
-        <f>(F30/F$36)*C$36</f>
-        <v>112.94155980763514</v>
-      </c>
-      <c r="H30">
-        <f>I8+I9+I10+I11</f>
-        <v>203.15406038952676</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B31">
-        <v>1970</v>
       </c>
       <c r="C31">
         <f>H8+H9+H10+H11</f>
         <v>150.88</v>
       </c>
-      <c r="D31">
-        <f>sources_consumption!D24</f>
-        <v>45177.14285714287</v>
+      <c r="E31">
+        <f>_xlfn.FORECAST.LINEAR(B31,D$27:D$32,B$27:B$32)</f>
+        <v>44674.938775510236</v>
       </c>
       <c r="F31">
-        <f>(D31/D$36)*F$36</f>
-        <v>110.30085738873842</v>
+        <f>(E31/D$37)*F$37</f>
+        <v>109.0747165288933</v>
       </c>
       <c r="G31">
-        <f>(F31/F$36)*C$36</f>
-        <v>111.18326424784834</v>
+        <f t="shared" si="2"/>
+        <v>109.94731426112448</v>
       </c>
       <c r="H31">
         <f>I8+I9+I10+I11</f>
-        <v>203.15406038952676</v>
+        <v>190.1656829749333</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32">
+        <v>1970</v>
+      </c>
+      <c r="C32">
+        <f>H8+H9+H10+H11</f>
+        <v>150.88</v>
+      </c>
+      <c r="D32">
+        <f>sources_consumption!D30</f>
+        <v>45177.14285714287</v>
+      </c>
+      <c r="F32">
+        <f>(D32/D$37)*F$37</f>
+        <v>110.30085738873842</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="2"/>
+        <v>111.18326424784834</v>
+      </c>
+      <c r="H32">
+        <f>I8+I9+I10+I11</f>
+        <v>190.1656829749333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B33" s="1">
         <v>1975</v>
-      </c>
-      <c r="C32">
-        <f>H10+H11</f>
-        <v>95.2</v>
-      </c>
-      <c r="E32">
-        <f>_xlfn.FORECAST.LINEAR(B32,D$31:D$36,B$31:B$36)</f>
-        <v>44473.970163809601</v>
-      </c>
-      <c r="F32">
-        <f>(E32/D$36)*F$36</f>
-        <v>108.58404782394886</v>
-      </c>
-      <c r="G32">
-        <f>(F32/F$36)*C$36</f>
-        <v>109.45272020654046</v>
-      </c>
-      <c r="H32">
-        <f>I10+I11</f>
-        <v>105.29154677574164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B33">
-        <v>1980</v>
       </c>
       <c r="C33">
         <f>H10+H11</f>
         <v>95.2</v>
       </c>
       <c r="E33">
-        <f>_xlfn.FORECAST.LINEAR(B33,D$31:D$36,B$31:B$36)</f>
-        <v>43770.797470476246</v>
+        <f>_xlfn.FORECAST.LINEAR(B33,D$32:D$37,B$32:B$37)</f>
+        <v>44473.970163809601</v>
       </c>
       <c r="F33">
-        <f>(E33/D$36)*F$36</f>
-        <v>106.86723825915907</v>
+        <f>(E33/D$37)*F$37</f>
+        <v>108.58404782394886</v>
       </c>
       <c r="G33">
-        <f>(F33/F$36)*C$36</f>
-        <v>107.72217616523236</v>
+        <f t="shared" si="2"/>
+        <v>109.45272020654046</v>
       </c>
       <c r="H33">
         <f>I10+I11</f>
-        <v>105.29154677574164</v>
+        <v>98.641353364710866</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B34">
+        <v>1980</v>
+      </c>
+      <c r="C34">
+        <f>H10+H11</f>
+        <v>95.2</v>
+      </c>
+      <c r="E34">
+        <f>_xlfn.FORECAST.LINEAR(B34,D$32:D$37,B$32:B$37)</f>
+        <v>43770.797470476246</v>
+      </c>
+      <c r="F34">
+        <f>(E34/D$37)*F$37</f>
+        <v>106.86723825915907</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="2"/>
+        <v>107.72217616523236</v>
+      </c>
+      <c r="H34">
+        <f>I10+I11</f>
+        <v>98.641353364710866</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B35">
         <v>1982</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <f>H11</f>
         <v>85.12</v>
       </c>
-      <c r="E34">
-        <f>_xlfn.FORECAST.LINEAR(B34,D$31:D$36,B$31:B$36)</f>
+      <c r="E35">
+        <f>_xlfn.FORECAST.LINEAR(B35,D$32:D$37,B$32:B$37)</f>
         <v>43489.528393142915</v>
       </c>
-      <c r="F34">
-        <f>(E34/D$36)*F$36</f>
+      <c r="F35">
+        <f>(E35/D$37)*F$37</f>
         <v>106.18051443324319</v>
       </c>
-      <c r="G34">
-        <f>(F34/F$36)*C$36</f>
+      <c r="G35">
+        <f t="shared" si="2"/>
         <v>107.02995854870915</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <f>I11</f>
-        <v>97.863608655259725</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1998</v>
-      </c>
-      <c r="C35">
-        <f>H12+H13</f>
-        <v>100.80000000000001</v>
-      </c>
-      <c r="E35">
-        <f>_xlfn.FORECAST.LINEAR(B35,D$31:D$36,B$31:B$36)</f>
-        <v>41239.375774476212</v>
-      </c>
-      <c r="F35">
-        <f>(E35/D$36)*F$36</f>
-        <v>100.68672382591595</v>
-      </c>
-      <c r="G35">
-        <f>(F35/F$36)*C$36</f>
-        <v>101.49221761652329</v>
-      </c>
-      <c r="H35">
-        <f>I12+I13</f>
-        <v>101.26147841101553</v>
+        <v>91.295986664338812</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>151</v>
-      </c>
-      <c r="B36">
-        <v>2000</v>
+        <v>30</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1998</v>
       </c>
       <c r="C36">
         <f>H12+H13</f>
         <v>100.80000000000001</v>
       </c>
-      <c r="D36">
-        <f>sources_consumption!D31</f>
+      <c r="E36">
+        <f>_xlfn.FORECAST.LINEAR(B36,D$32:D$37,B$32:B$37)</f>
+        <v>41239.375774476212</v>
+      </c>
+      <c r="F36">
+        <f>(E36/D$37)*F$37</f>
+        <v>100.68672382591595</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="2"/>
+        <v>101.49221761652329</v>
+      </c>
+      <c r="H36">
+        <f>I12+I13</f>
+        <v>101.26147841101553</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37">
+        <v>2000</v>
+      </c>
+      <c r="C37">
+        <f>H12+H13</f>
+        <v>100.80000000000001</v>
+      </c>
+      <c r="D37">
+        <f>sources_consumption!D37</f>
         <v>40958.106697142859</v>
       </c>
-      <c r="F36">
+      <c r="F37">
         <v>100</v>
       </c>
-      <c r="G36">
-        <f>(F36/F$36)*C$36</f>
+      <c r="G37">
+        <f t="shared" si="2"/>
         <v>100.80000000000001</v>
       </c>
-      <c r="H36">
-        <f>I11+I13</f>
-        <v>165.52508706627526</v>
+      <c r="H37">
+        <f>I12+I13</f>
+        <v>101.26147841101553</v>
       </c>
     </row>
   </sheetData>
@@ -10100,7 +10373,7 @@
         <v>1962.5</v>
       </c>
       <c r="E5">
-        <f>dist_calculations!E22</f>
+        <f>dist_calculations!E25</f>
         <v>8</v>
       </c>
       <c r="F5">
@@ -10133,7 +10406,7 @@
         <v>1975</v>
       </c>
       <c r="E6">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F6">
@@ -10198,7 +10471,7 @@
         <v>2000</v>
       </c>
       <c r="E8">
-        <f>dist_calculations!E28</f>
+        <f>dist_calculations!E31</f>
         <v>15</v>
       </c>
       <c r="F8">
@@ -10232,7 +10505,7 @@
         <v>1997.5</v>
       </c>
       <c r="E9">
-        <f>dist_calculations!E29</f>
+        <f>dist_calculations!E32</f>
         <v>10</v>
       </c>
       <c r="F9">
@@ -10308,7 +10581,7 @@
         <v>27.675071428571428</v>
       </c>
       <c r="G13">
-        <f>(F13/F$29)*C$29</f>
+        <f t="shared" ref="G13:G29" si="3">(F13/F$29)*C$29</f>
         <v>48.818825999999994</v>
       </c>
       <c r="H13">
@@ -10333,7 +10606,7 @@
         <v>24.723063636363658</v>
       </c>
       <c r="G14">
-        <f>(F14/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>43.611484254545488</v>
       </c>
       <c r="H14">
@@ -10354,7 +10627,7 @@
         <v>20.295051948051945</v>
       </c>
       <c r="G15">
-        <f>(F15/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>35.800471636363625</v>
       </c>
       <c r="H15">
@@ -10379,7 +10652,7 @@
         <v>50.276381764069221</v>
       </c>
       <c r="G16">
-        <f>(F16/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>88.6875374318181</v>
       </c>
       <c r="H16">
@@ -10404,7 +10677,7 @@
         <v>80.257711580086593</v>
       </c>
       <c r="G17">
-        <f>(F17/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>141.57460322727272</v>
       </c>
       <c r="H17">
@@ -10429,7 +10702,7 @@
         <v>92.250243506493504</v>
       </c>
       <c r="G18">
-        <f>(F18/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>162.72942954545451</v>
       </c>
       <c r="H18">
@@ -10454,7 +10727,7 @@
         <v>88.454804916512103</v>
       </c>
       <c r="G19">
-        <f>(F19/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>156.03427587272731</v>
       </c>
       <c r="H19">
@@ -10479,7 +10752,7 @@
         <v>86.97880102040817</v>
       </c>
       <c r="G20">
-        <f>(F20/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>153.43060499999999</v>
       </c>
       <c r="H20">
@@ -10504,7 +10777,7 @@
         <v>100.38332619931079</v>
       </c>
       <c r="G21">
-        <f>(F21/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>177.0761874155842</v>
       </c>
       <c r="H21">
@@ -10529,7 +10802,7 @@
         <v>120.49011396766485</v>
       </c>
       <c r="G22">
-        <f>(F22/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>212.54456103896075</v>
       </c>
       <c r="H22">
@@ -10554,7 +10827,7 @@
         <v>123.17101900344565</v>
       </c>
       <c r="G23">
-        <f>(F23/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>217.27367752207809</v>
       </c>
       <c r="H23">
@@ -10571,7 +10844,7 @@
         <v>74.48</v>
       </c>
       <c r="D24">
-        <f>sources_consumption!D29</f>
+        <f>sources_consumption!D35</f>
         <v>3299.1639085714291</v>
       </c>
       <c r="F24">
@@ -10579,7 +10852,7 @@
         <v>133.89463914656773</v>
       </c>
       <c r="G24">
-        <f>(F24/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>236.19014345454542</v>
       </c>
       <c r="H24">
@@ -10604,7 +10877,7 @@
         <v>128.24553262213959</v>
       </c>
       <c r="G25">
-        <f>(F25/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>226.22511954545422</v>
       </c>
       <c r="H25">
@@ -10629,7 +10902,7 @@
         <v>116.94731957328382</v>
       </c>
       <c r="G26">
-        <f>(F26/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>206.29507172727261</v>
       </c>
       <c r="H26">
@@ -10654,7 +10927,7 @@
         <v>109.03857043908474</v>
       </c>
       <c r="G27">
-        <f>(F27/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>192.34403825454544</v>
       </c>
       <c r="H27">
@@ -10679,7 +10952,7 @@
         <v>102.25964260977103</v>
       </c>
       <c r="G28">
-        <f>(F28/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>180.38600956363607</v>
       </c>
       <c r="H28">
@@ -10696,14 +10969,14 @@
         <v>176.39999999999998</v>
       </c>
       <c r="D29">
-        <f>sources_consumption!D36</f>
+        <f>sources_consumption!D42</f>
         <v>2464</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <f>(F29/F$29)*C$29</f>
+        <f t="shared" si="3"/>
         <v>176.39999999999998</v>
       </c>
       <c r="H29">
@@ -10789,8 +11062,8 @@
         <v>15</v>
       </c>
       <c r="I2">
-        <f>(G18/C18)*H2</f>
-        <v>197.66064034529006</v>
+        <f>(G20/C20)*H2</f>
+        <v>28.464668020376386</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10821,8 +11094,8 @@
         <v>54</v>
       </c>
       <c r="I3">
-        <f>((G20)/H3)*H3</f>
-        <v>242.47904135381546</v>
+        <f>((G20)/C20)*H3</f>
+        <v>102.472804873355</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -10854,7 +11127,7 @@
       </c>
       <c r="I4">
         <f>(G23/C23)*H4</f>
-        <v>36.436075631365064</v>
+        <v>24.007125768386146</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10886,7 +11159,7 @@
       </c>
       <c r="I5">
         <f>(G23/C23)*H5</f>
-        <v>273.27056723523793</v>
+        <v>180.05344326289611</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -10918,7 +11191,7 @@
       </c>
       <c r="I6">
         <f>(G27/C27)*H6</f>
-        <v>7.2688937940497906</v>
+        <v>5.3793890091180065</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -10950,7 +11223,7 @@
       </c>
       <c r="I7">
         <f>(G27/C27)*H7</f>
-        <v>381.61692418761402</v>
+        <v>282.41792297869534</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -10982,7 +11255,7 @@
       </c>
       <c r="I8">
         <f>(G31/C31)*H8</f>
-        <v>2.8810030043836643</v>
+        <v>2.5454768386781073</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -11046,7 +11319,7 @@
       </c>
       <c r="I10">
         <f>(G32/C32)*H10</f>
-        <v>3.2657654825778981</v>
+        <v>3.089614245582486</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -11064,7 +11337,7 @@
         <v>1975</v>
       </c>
       <c r="E11">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F11">
@@ -11097,7 +11370,7 @@
         <v>2000</v>
       </c>
       <c r="E12">
-        <f>dist_calculations!E$28</f>
+        <f>dist_calculations!E$31</f>
         <v>15</v>
       </c>
       <c r="F12">
@@ -11131,7 +11404,7 @@
         <v>1997.5</v>
       </c>
       <c r="E13">
-        <f>dist_calculations!E$29</f>
+        <f>dist_calculations!E$32</f>
         <v>10</v>
       </c>
       <c r="F13">
@@ -11190,17 +11463,20 @@
         <f>H2</f>
         <v>15</v>
       </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
       <c r="E17">
         <f>_xlfn.FORECAST.LINEAR(B17,D$25:D$28,B$25:B$28)</f>
-        <v>3820.3128258602665</v>
+        <v>2827.245714285702</v>
       </c>
       <c r="F17">
-        <f>(E17/D$39)*100</f>
-        <v>58.138678643537325</v>
+        <f t="shared" ref="F17:F24" si="2">(E17/D$39)*100</f>
+        <v>43.025882309038614</v>
       </c>
       <c r="G17">
-        <f>(F17/F$39)*C$39</f>
-        <v>122.96330533108144</v>
+        <f t="shared" ref="G17:G38" si="3">(F17/F$39)*C$39</f>
+        <v>90.999741083616669</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
@@ -11212,20 +11488,20 @@
         <v>15</v>
       </c>
       <c r="E18">
-        <f>_xlfn.FORECAST.LINEAR(B18,D$25:D$28,B$25:B$28)</f>
-        <v>6141.0636079249234</v>
+        <f>_xlfn.FORECAST.LINEAR(B18,D$17:D$28,B$17:B$28)</f>
+        <v>2553.4992319508456</v>
       </c>
       <c r="F18">
-        <f>(E18/D$39)*100</f>
-        <v>93.456567539144245</v>
+        <f t="shared" si="2"/>
+        <v>38.859925359510235</v>
       </c>
       <c r="G18">
-        <f>(F18/F$39)*C$39</f>
-        <v>197.66064034529006</v>
+        <f t="shared" si="3"/>
+        <v>82.188742135364137</v>
       </c>
       <c r="H18">
         <f>I2</f>
-        <v>197.66064034529006</v>
+        <v>28.464668020376386</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
@@ -11237,16 +11513,16 @@
         <v>69</v>
       </c>
       <c r="E19">
-        <f>_xlfn.FORECAST.LINEAR(B19,D$25:D$28,B$25:B$28)</f>
-        <v>6976.5338894682063</v>
+        <f>_xlfn.FORECAST.LINEAR(B19,D$17:D$28,B$17:B$28)</f>
+        <v>3462.2357083776442</v>
       </c>
       <c r="F19">
-        <f>(E19/D$39)*100</f>
-        <v>106.17100754156283</v>
+        <f t="shared" si="2"/>
+        <v>52.689352525004487</v>
       </c>
       <c r="G19">
-        <f>(F19/F$39)*C$39</f>
-        <v>224.5516809504054</v>
+        <f t="shared" si="3"/>
+        <v>111.43798059038448</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -11258,20 +11534,20 @@
         <v>69</v>
       </c>
       <c r="E20">
-        <f>_xlfn.FORECAST.LINEAR(B20,D$25:D$28,B$25:B$28)</f>
-        <v>7533.5140771637234</v>
+        <f>_xlfn.FORECAST.LINEAR(B20,D$17:D$28,B$17:B$28)</f>
+        <v>4068.0600259955099</v>
       </c>
       <c r="F20">
-        <f>(E20/D$39)*100</f>
-        <v>114.64730087650847</v>
+        <f t="shared" si="2"/>
+        <v>61.908970635333979</v>
       </c>
       <c r="G20">
-        <f>(F20/F$39)*C$39</f>
-        <v>242.47904135381543</v>
+        <f t="shared" si="3"/>
+        <v>130.93747289373138</v>
       </c>
       <c r="H20">
         <f>I2+I3</f>
-        <v>440.13968169910549</v>
+        <v>130.93747289373138</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
@@ -11283,16 +11559,16 @@
         <v>69</v>
       </c>
       <c r="E21">
-        <f>_xlfn.FORECAST.LINEAR(B21,D$25:D$28,B$25:B$28)</f>
-        <v>7997.6642335766519</v>
+        <f>_xlfn.FORECAST.LINEAR(B21,D$17:D$28,B$17:B$28)</f>
+        <v>4572.9136240103981</v>
       </c>
       <c r="F21">
-        <f>(E21/D$39)*100</f>
-        <v>121.71087865562981</v>
+        <f t="shared" si="2"/>
+        <v>69.59198572727523</v>
       </c>
       <c r="G21">
-        <f>(F21/F$39)*C$39</f>
-        <v>257.41850835665707</v>
+        <f t="shared" si="3"/>
+        <v>147.18704981318712</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
@@ -11304,16 +11580,16 @@
         <v>153</v>
       </c>
       <c r="E22">
-        <f>_xlfn.FORECAST.LINEAR(B22,D$25:D$28,B$25:B$28)</f>
-        <v>8044.0792492179462</v>
+        <f>_xlfn.FORECAST.LINEAR(B22,D$17:D$28,B$17:B$28)</f>
+        <v>4623.3989838118869</v>
       </c>
       <c r="F22">
-        <f>(E22/D$39)*100</f>
-        <v>122.41723643354199</v>
+        <f t="shared" si="2"/>
+        <v>70.360287236469361</v>
       </c>
       <c r="G22">
-        <f>(F22/F$39)*C$39</f>
-        <v>258.91245505694133</v>
+        <f t="shared" si="3"/>
+        <v>148.8120075051327</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
@@ -11325,20 +11601,20 @@
         <v>153</v>
       </c>
       <c r="E23">
-        <f>_xlfn.FORECAST.LINEAR(B23,D$25:D$28,B$25:B$28)</f>
-        <v>9622.1897810219089</v>
+        <f>_xlfn.FORECAST.LINEAR(B23,D$17:D$28,B$17:B$28)</f>
+        <v>6339.9012170625065</v>
       </c>
       <c r="F23">
-        <f>(E23/D$39)*100</f>
-        <v>146.43340088255462</v>
+        <f t="shared" si="2"/>
+        <v>96.482538549069602</v>
       </c>
       <c r="G23">
-        <f>(F23/F$39)*C$39</f>
-        <v>309.70664286660303</v>
+        <f t="shared" si="3"/>
+        <v>204.06056903128223</v>
       </c>
       <c r="H23">
         <f>I4+I5</f>
-        <v>309.70664286660298</v>
+        <v>204.06056903128226</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
@@ -11350,16 +11626,16 @@
         <v>153</v>
       </c>
       <c r="E24">
-        <f>_xlfn.FORECAST.LINEAR(B24,D$25:D$28,B$25:B$28)</f>
-        <v>10782.565172054237</v>
+        <f>_xlfn.FORECAST.LINEAR(B24,D$17:D$28,B$17:B$28)</f>
+        <v>7602.0352120997268</v>
       </c>
       <c r="F24">
-        <f>(E24/D$39)*100</f>
-        <v>164.09234533035809</v>
+        <f t="shared" si="2"/>
+        <v>115.69007627892273</v>
       </c>
       <c r="G24">
-        <f>(F24/F$39)*C$39</f>
-        <v>347.05531037370736</v>
+        <f t="shared" si="3"/>
+        <v>244.68451132992158</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
@@ -11372,15 +11648,15 @@
       </c>
       <c r="D25">
         <f>sources_consumption!D13</f>
-        <v>11246.715328467153</v>
+        <v>8323.1999999999989</v>
       </c>
       <c r="F25">
         <f>(D25/D$39)*100</f>
-        <v>171.15592310947923</v>
+        <v>126.66498062941326</v>
       </c>
       <c r="G25">
-        <f>(F25/F$39)*C$39</f>
-        <v>361.99477737654854</v>
+        <f t="shared" si="3"/>
+        <v>267.89643403120908</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
@@ -11393,15 +11669,15 @@
       </c>
       <c r="E26">
         <f>_xlfn.FORECAST.LINEAR(B26,D$25:D$28,B$25:B$28)</f>
-        <v>11293.13034410846</v>
+        <v>8357.549714285713</v>
       </c>
       <c r="F26">
         <f>(E26/D$39)*100</f>
-        <v>171.86228088739156</v>
+        <v>127.18772499391562</v>
       </c>
       <c r="G26">
-        <f>(F26/F$39)*C$39</f>
-        <v>363.48872407683319</v>
+        <f t="shared" si="3"/>
+        <v>269.00203836213154</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
@@ -11414,19 +11690,19 @@
       </c>
       <c r="E27">
         <f>_xlfn.FORECAST.LINEAR(B27,D$25:D$28,B$25:B$28)</f>
-        <v>12082.185610010434</v>
+        <v>8941.4948571428613</v>
       </c>
       <c r="F27">
         <f>(E27/D$39)*100</f>
-        <v>183.8703631118978</v>
+        <v>136.07437919045549</v>
       </c>
       <c r="G27">
-        <f>(F27/F$39)*C$39</f>
-        <v>388.88581798166382</v>
+        <f t="shared" si="3"/>
+        <v>287.79731198781337</v>
       </c>
       <c r="H27">
         <f>I6+I7</f>
-        <v>388.88581798166382</v>
+        <v>287.79731198781337</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
@@ -11439,15 +11715,15 @@
       </c>
       <c r="D28">
         <f>sources_consumption!D19</f>
-        <v>12407.09071949948</v>
+        <v>9181.942857142858</v>
       </c>
       <c r="F28">
         <f>(D28/D$39)*100</f>
-        <v>188.81486755728267</v>
+        <v>139.73358974197183</v>
       </c>
       <c r="G28">
-        <f>(F28/F$39)*C$39</f>
-        <v>399.34344488365286</v>
+        <f t="shared" si="3"/>
+        <v>295.53654230427043</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
@@ -11460,15 +11736,15 @@
       </c>
       <c r="E29">
         <f>_xlfn.FORECAST.LINEAR(B29,D$28:D$33,B$28:B$33)</f>
-        <v>10429.352003575186</v>
+        <v>8217.8220408163324</v>
       </c>
       <c r="F29">
         <f>(E29/D$39)*100</f>
-        <v>158.71704026218086</v>
+        <v>125.06130690311015</v>
       </c>
       <c r="G29">
-        <f>(F29/F$39)*C$39</f>
-        <v>335.6865401545125</v>
+        <f t="shared" si="3"/>
+        <v>264.50466410007795</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
@@ -11480,16 +11756,16 @@
         <v>185.55</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30:E32" si="2">_xlfn.FORECAST.LINEAR(B30,D$28:D$33,B$28:B$33)</f>
-        <v>9710.1742886935826</v>
+        <f t="shared" ref="E30:E32" si="4">_xlfn.FORECAST.LINEAR(B30,D$28:D$33,B$28:B$33)</f>
+        <v>7867.232653061219</v>
       </c>
       <c r="F30">
         <f>(E30/D$39)*100</f>
-        <v>147.77237579123411</v>
+        <v>119.72593132534206</v>
       </c>
       <c r="G30">
-        <f>(F30/F$39)*C$39</f>
-        <v>312.5385747984601</v>
+        <f t="shared" si="3"/>
+        <v>253.22034475309846</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.25">
@@ -11501,20 +11777,20 @@
         <v>212.15</v>
       </c>
       <c r="E31">
-        <f t="shared" si="2"/>
-        <v>7912.2300014896318</v>
+        <f t="shared" si="4"/>
+        <v>6990.75918367345</v>
       </c>
       <c r="F31">
         <f>(E31/D$39)*100</f>
-        <v>120.41071461386809</v>
+        <v>106.38749238092208</v>
       </c>
       <c r="G31">
-        <f>(F31/F$39)*C$39</f>
-        <v>254.66866140833102</v>
+        <f t="shared" si="3"/>
+        <v>225.00954638565022</v>
       </c>
       <c r="H31">
         <f>I8+I9+I10</f>
-        <v>178.39675532082472</v>
+        <v>177.88507791812373</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
@@ -11526,20 +11802,20 @@
         <v>212.15</v>
       </c>
       <c r="E32">
-        <f t="shared" si="2"/>
-        <v>6833.4634291672846</v>
+        <f t="shared" si="4"/>
+        <v>6464.8751020408235</v>
       </c>
       <c r="F32">
         <f>(E32/D$39)*100</f>
-        <v>103.99371790744884</v>
+        <v>98.384429014270623</v>
       </c>
       <c r="G32">
-        <f>(F32/F$39)*C$39</f>
-        <v>219.9467133742543</v>
+        <f t="shared" si="3"/>
+        <v>208.08306736518236</v>
       </c>
       <c r="H32">
         <f>I8+I9+I10+I11</f>
-        <v>203.66503778917672</v>
+        <v>203.15336038647573</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
@@ -11551,7 +11827,7 @@
         <v>212.15</v>
       </c>
       <c r="D33">
-        <f>sources_consumption!D25</f>
+        <f>sources_consumption!D31</f>
         <v>6114.2857142857147</v>
       </c>
       <c r="F33">
@@ -11559,7 +11835,7 @@
         <v>93.049053436502604</v>
       </c>
       <c r="G33">
-        <f>(F33/F$39)*C$39</f>
+        <f t="shared" si="3"/>
         <v>196.79874801820301</v>
       </c>
     </row>
@@ -11580,12 +11856,12 @@
         <v>94.207544530418843</v>
       </c>
       <c r="G34">
-        <f>(F34/F$39)*C$39</f>
+        <f t="shared" si="3"/>
         <v>199.24895668183584</v>
       </c>
       <c r="H34">
         <f>I9+I10+I11</f>
-        <v>200.78403478479305</v>
+        <v>200.60788354779763</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
@@ -11605,12 +11881,12 @@
         <v>94.902639186768567</v>
       </c>
       <c r="G35">
-        <f>(F35/F$39)*C$39</f>
+        <f t="shared" si="3"/>
         <v>200.71908188001552</v>
       </c>
       <c r="H35">
         <f>I9+I10+I11</f>
-        <v>200.78403478479305</v>
+        <v>200.60788354779763</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
@@ -11630,7 +11906,7 @@
         <v>95.829432061901571</v>
       </c>
       <c r="G36">
-        <f>(F36/F$39)*C$39</f>
+        <f t="shared" si="3"/>
         <v>202.67924881092182</v>
       </c>
     </row>
@@ -11651,7 +11927,7 @@
         <v>96.524526718251295</v>
       </c>
       <c r="G37">
-        <f>(F37/F$39)*C$39</f>
+        <f t="shared" si="3"/>
         <v>204.14937400910148</v>
       </c>
     </row>
@@ -11672,7 +11948,7 @@
         <v>99.536603562433527</v>
       </c>
       <c r="G38">
-        <f>(F38/F$39)*C$39</f>
+        <f t="shared" si="3"/>
         <v>210.51991653454689</v>
       </c>
       <c r="H38">
@@ -11689,7 +11965,7 @@
         <v>211.5</v>
       </c>
       <c r="D39">
-        <f>sources_consumption!D32</f>
+        <f>sources_consumption!D38</f>
         <v>6571.0348342857142</v>
       </c>
       <c r="F39">
@@ -11779,7 +12055,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <f xml:space="preserve"> E2*F2*G2/100</f>
+        <f t="shared" ref="H2:H9" si="0" xml:space="preserve"> E2*F2*G2/100</f>
         <v>32</v>
       </c>
       <c r="I2">
@@ -11811,7 +12087,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <f xml:space="preserve"> E3*F3*G3/100</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="I3">
@@ -11843,7 +12119,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <f xml:space="preserve"> E4*F4*G4/100</f>
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="I4">
@@ -11875,7 +12151,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <f xml:space="preserve"> E5*F5*G5/100</f>
+        <f t="shared" si="0"/>
         <v>96</v>
       </c>
       <c r="I5">
@@ -11907,7 +12183,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <f xml:space="preserve"> E6*F6*G6/100</f>
+        <f t="shared" si="0"/>
         <v>5.04</v>
       </c>
       <c r="I6">
@@ -11929,7 +12205,7 @@
         <v>1975</v>
       </c>
       <c r="E7">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F7">
@@ -11939,7 +12215,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <f xml:space="preserve"> E7*F7*G7/100</f>
+        <f t="shared" si="0"/>
         <v>42.56</v>
       </c>
       <c r="I7">
@@ -11958,11 +12234,11 @@
         <v>2010</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8" si="0" xml:space="preserve"> (B8+C8)/2</f>
+        <f t="shared" ref="D8" si="1" xml:space="preserve"> (B8+C8)/2</f>
         <v>2000</v>
       </c>
       <c r="E8">
-        <f>dist_calculations!E$28</f>
+        <f>dist_calculations!E$31</f>
         <v>15</v>
       </c>
       <c r="F8">
@@ -11973,7 +12249,7 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <f xml:space="preserve"> E8*F8*G8/100</f>
+        <f t="shared" si="0"/>
         <v>16.8</v>
       </c>
       <c r="I8">
@@ -11996,7 +12272,7 @@
         <v>1997.5</v>
       </c>
       <c r="E9">
-        <f>dist_calculations!E$29</f>
+        <f>dist_calculations!E$32</f>
         <v>10</v>
       </c>
       <c r="F9">
@@ -12006,7 +12282,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <f xml:space="preserve"> E9*F9*G9/100</f>
+        <f t="shared" si="0"/>
         <v>33.6</v>
       </c>
       <c r="I9">
@@ -12068,11 +12344,11 @@
         <v>153600</v>
       </c>
       <c r="F17">
-        <f>(E17/D$31)*F$31</f>
+        <f t="shared" ref="F17:F22" si="2">(E17/D$31)*F$31</f>
         <v>212.85900103839083</v>
       </c>
       <c r="G17">
-        <f>(F17/F$31)*C$31</f>
+        <f t="shared" ref="G17:G31" si="3">(F17/F$31)*C$31</f>
         <v>107.280936523349</v>
       </c>
       <c r="H17">
@@ -12093,11 +12369,11 @@
         <v>147200</v>
       </c>
       <c r="F18">
-        <f>(E18/D$31)*F$31</f>
+        <f t="shared" si="2"/>
         <v>203.98987599512455</v>
       </c>
       <c r="G18">
-        <f>(F18/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>102.81089750154278</v>
       </c>
       <c r="H18">
@@ -12118,11 +12394,11 @@
         <v>140480</v>
       </c>
       <c r="F19">
-        <f>(E19/D$31)*F$31</f>
+        <f t="shared" si="2"/>
         <v>194.67729469969495</v>
       </c>
       <c r="G19">
-        <f>(F19/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>98.117356528646269</v>
       </c>
       <c r="H19">
@@ -12143,11 +12419,11 @@
         <v>129600</v>
       </c>
       <c r="F20">
-        <f>(E20/D$31)*F$31</f>
+        <f t="shared" si="2"/>
         <v>179.59978212614226</v>
       </c>
       <c r="G20">
-        <f>(F20/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>90.518290191575701</v>
       </c>
       <c r="H20">
@@ -12172,11 +12448,11 @@
         <v>128000</v>
       </c>
       <c r="F21">
-        <f>(E21/D$31)*F$31</f>
+        <f t="shared" si="2"/>
         <v>177.38250086532571</v>
       </c>
       <c r="G21">
-        <f>(F21/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>89.40078043612418</v>
       </c>
       <c r="H21">
@@ -12197,11 +12473,11 @@
         <v>96914.285714285914</v>
       </c>
       <c r="F22">
-        <f>(E22/D$31)*F$31</f>
+        <f t="shared" si="2"/>
         <v>134.3038935123183</v>
       </c>
       <c r="G22">
-        <f>(F22/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>67.689162330208433</v>
       </c>
       <c r="H22">
@@ -12226,7 +12502,7 @@
         <v>112.76458983581421</v>
       </c>
       <c r="G23">
-        <f>(F23/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>56.833353277250367</v>
       </c>
       <c r="H23">
@@ -12251,7 +12527,7 @@
         <v>105.238503727671</v>
       </c>
       <c r="G24">
-        <f>(F24/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>53.040205878746193</v>
       </c>
       <c r="H24">
@@ -12276,7 +12552,7 @@
         <v>102.3116924633932</v>
       </c>
       <c r="G25">
-        <f>(F25/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>51.565093001550181</v>
       </c>
       <c r="H25">
@@ -12301,7 +12577,7 @@
         <v>100.71660747474456</v>
       </c>
       <c r="G26">
-        <f>(F26/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>50.76117016727126</v>
       </c>
       <c r="H26">
@@ -12326,7 +12602,7 @@
         <v>100.33378707746887</v>
       </c>
       <c r="G27">
-        <f>(F27/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>50.568228687044318</v>
       </c>
       <c r="H27">
@@ -12343,7 +12619,7 @@
         <v>143.60000000000002</v>
       </c>
       <c r="D28">
-        <f>sources_consumption!D26</f>
+        <f>sources_consumption!D32</f>
         <v>72217.14285714287</v>
       </c>
       <c r="F28">
@@ -12351,7 +12627,7 @@
         <v>100.0785734792851</v>
       </c>
       <c r="G28">
-        <f>(F28/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>50.439601033559697</v>
       </c>
       <c r="H28">
@@ -12376,7 +12652,7 @@
         <v>100.06547789940427</v>
       </c>
       <c r="G29">
-        <f>(F29/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>50.43300086129976</v>
       </c>
       <c r="H29">
@@ -12401,7 +12677,7 @@
         <v>100.00523823195235</v>
       </c>
       <c r="G30">
-        <f>(F30/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>50.402640068903992</v>
       </c>
       <c r="H30">
@@ -12418,14 +12694,14 @@
         <v>50.400000000000006</v>
       </c>
       <c r="D31">
-        <f>sources_consumption!D33</f>
+        <f>sources_consumption!D39</f>
         <v>72160.443885714281</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <f>(F31/F$31)*C$31</f>
+        <f t="shared" si="3"/>
         <v>50.400000000000006</v>
       </c>
       <c r="H31">
@@ -12540,8 +12816,8 @@
         <v>27</v>
       </c>
       <c r="I3">
-        <f>(G$19/C$19)*H3</f>
-        <v>23.700316298826298</v>
+        <f>((G$19)/(C$19-I2))*H3</f>
+        <v>35.616020468703105</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -12783,7 +13059,7 @@
         <v>1975</v>
       </c>
       <c r="E11">
-        <f>dist_calculations!E$24</f>
+        <f>dist_calculations!E$27</f>
         <v>38</v>
       </c>
       <c r="F11">
@@ -12816,7 +13092,7 @@
         <v>2000</v>
       </c>
       <c r="E12">
-        <f>dist_calculations!E$28</f>
+        <f>dist_calculations!E$31</f>
         <v>15</v>
       </c>
       <c r="F12">
@@ -12850,7 +13126,7 @@
         <v>1997.5</v>
       </c>
       <c r="E13">
-        <f>dist_calculations!E$29</f>
+        <f>dist_calculations!E$32</f>
         <v>10</v>
       </c>
       <c r="F13">
@@ -12928,7 +13204,7 @@
         <v>20.55669645334962</v>
       </c>
       <c r="G18">
-        <f>(F18/F$33)*C$33</f>
+        <f t="shared" ref="G18:G33" si="2">(F18/F$33)*C$33</f>
         <v>40.147228173391809</v>
       </c>
       <c r="H18">
@@ -12956,16 +13232,16 @@
         <v>53.934838251866189</v>
       </c>
       <c r="G19">
-        <f>(F19/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>105.33473910589466</v>
       </c>
       <c r="H19">
         <f>I2+I3</f>
-        <v>63.847544472218104</v>
+        <v>75.763248642094908</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11">
+      <c r="B20">
         <v>1850</v>
       </c>
       <c r="C20">
@@ -12981,7 +13257,7 @@
         <v>73.53654746007706</v>
       </c>
       <c r="G20">
-        <f>(F20/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>143.6168771895305</v>
       </c>
       <c r="H20">
@@ -13009,7 +13285,7 @@
         <v>96.438061857772496</v>
       </c>
       <c r="G21">
-        <f>(F21/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>188.34353480822966</v>
       </c>
       <c r="H21">
@@ -13034,7 +13310,7 @@
         <v>119.3395762554682</v>
       </c>
       <c r="G22">
-        <f>(F22/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>233.0701924269294</v>
       </c>
       <c r="H22">
@@ -13059,7 +13335,7 @@
         <v>128.50018201454648</v>
       </c>
       <c r="G23">
-        <f>(F23/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>250.96085547440924</v>
       </c>
       <c r="H23">
@@ -13087,7 +13363,7 @@
         <v>134.69998461071233</v>
       </c>
       <c r="G24">
-        <f>(F24/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>263.06906994472115</v>
       </c>
       <c r="H24">
@@ -13112,7 +13388,7 @@
         <v>137.11101895366559</v>
       </c>
       <c r="G25">
-        <f>(F25/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>267.77782001650888</v>
       </c>
       <c r="H25">
@@ -13140,7 +13416,7 @@
         <v>122.01839816477002</v>
       </c>
       <c r="G26">
-        <f>(F26/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>238.30193161579584</v>
       </c>
       <c r="H26">
@@ -13168,7 +13444,7 @@
         <v>118.39616917543509</v>
       </c>
       <c r="G27">
-        <f>(F27/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>231.22771839962473</v>
       </c>
       <c r="H27">
@@ -13185,7 +13461,7 @@
         <v>259.63</v>
       </c>
       <c r="D28">
-        <f>sources_consumption!D27</f>
+        <f>sources_consumption!D33</f>
         <v>100057.14285714286</v>
       </c>
       <c r="F28">
@@ -13193,7 +13469,7 @@
         <v>115.9813498492118</v>
       </c>
       <c r="G28">
-        <f>(F28/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>226.51157625551062</v>
       </c>
       <c r="H28">
@@ -13221,7 +13497,7 @@
         <v>113.31779154100998</v>
       </c>
       <c r="G29">
-        <f>(F29/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>221.30964687959246</v>
       </c>
       <c r="H29">
@@ -13246,7 +13522,7 @@
         <v>110.65423323280805</v>
       </c>
       <c r="G30">
-        <f>(F30/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>216.10771750367411</v>
       </c>
       <c r="H30">
@@ -13271,7 +13547,7 @@
         <v>109.58880990952721</v>
       </c>
       <c r="G31">
-        <f>(F31/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>214.02694575330665</v>
       </c>
       <c r="H31">
@@ -13299,7 +13575,7 @@
         <v>101.06542332328085</v>
       </c>
       <c r="G32">
-        <f>(F32/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>197.3807717503675</v>
       </c>
       <c r="H32">
@@ -13316,14 +13592,14 @@
         <v>195.29999999999998</v>
       </c>
       <c r="D33">
-        <f>sources_consumption!D34</f>
+        <f>sources_consumption!D40</f>
         <v>86270.027885714284</v>
       </c>
       <c r="F33">
         <v>100</v>
       </c>
       <c r="G33">
-        <f>(F33/F$33)*C$33</f>
+        <f t="shared" si="2"/>
         <v>195.29999999999998</v>
       </c>
       <c r="H33">
